--- a/SVTwello/zondag2.xlsx
+++ b/SVTwello/zondag2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rodi/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rodi/Documents/Zondag2/SVTwello/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8FBEF5F-77CD-014A-925C-EFE1F1B471FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2F3DDB-6020-414D-B147-265CF5588368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34560" yWindow="-5860" windowWidth="51200" windowHeight="28200" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="34560" windowHeight="20580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="spelers" sheetId="1" r:id="rId1"/>
@@ -222,9 +222,6 @@
     <t>SV Twello 2</t>
   </si>
   <si>
-    <t>0-3</t>
-  </si>
-  <si>
     <t>Beker</t>
   </si>
   <si>
@@ -646,6 +643,9 @@
   </si>
   <si>
     <t>Hoofdcoach</t>
+  </si>
+  <si>
+    <t>2-3</t>
   </si>
 </sst>
 </file>
@@ -681,8 +681,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -1020,7 +1021,7 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -1234,7 +1235,7 @@
         <v>24</v>
       </c>
       <c r="D12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
@@ -1577,7 +1578,7 @@
         <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1585,10 +1586,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1599,7 +1600,7 @@
         <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1610,7 +1611,7 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1621,7 +1622,7 @@
         <v>47</v>
       </c>
       <c r="C6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1632,7 +1633,7 @@
         <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -1692,202 +1693,211 @@
       <c r="E2" t="s">
         <v>59</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="G2" t="s">
         <v>60</v>
-      </c>
-      <c r="G2" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" t="s">
         <v>62</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>63</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" t="s">
         <v>64</v>
       </c>
-      <c r="D3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" t="s">
-        <v>65</v>
-      </c>
+      <c r="F3" s="1"/>
       <c r="G3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" t="s">
         <v>66</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" t="s">
         <v>67</v>
       </c>
-      <c r="C4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" t="s">
-        <v>68</v>
-      </c>
+      <c r="F4" s="1"/>
       <c r="G4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" t="s">
         <v>69</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>70</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>71</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" t="s">
         <v>72</v>
-      </c>
-      <c r="E5" t="s">
-        <v>59</v>
-      </c>
-      <c r="G5" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" t="s">
         <v>74</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" t="s">
         <v>75</v>
       </c>
-      <c r="C6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" t="s">
-        <v>76</v>
-      </c>
+      <c r="F6" s="1"/>
       <c r="G6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" t="s">
         <v>77</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" t="s">
         <v>78</v>
       </c>
-      <c r="C7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" t="s">
-        <v>79</v>
-      </c>
       <c r="E7" t="s">
         <v>59</v>
       </c>
+      <c r="F7" s="1"/>
       <c r="G7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" t="s">
         <v>80</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" t="s">
         <v>81</v>
       </c>
-      <c r="C8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" t="s">
-        <v>82</v>
-      </c>
+      <c r="F8" s="1"/>
       <c r="G8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" t="s">
         <v>83</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" t="s">
         <v>84</v>
       </c>
-      <c r="C9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" t="s">
-        <v>85</v>
-      </c>
+      <c r="F9" s="1"/>
       <c r="G9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" t="s">
         <v>86</v>
-      </c>
-      <c r="B10" t="s">
-        <v>87</v>
       </c>
       <c r="C10" t="s">
         <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
         <v>59</v>
       </c>
+      <c r="F10" s="1"/>
       <c r="G10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" t="s">
         <v>89</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" t="s">
         <v>90</v>
       </c>
-      <c r="C11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" t="s">
-        <v>91</v>
-      </c>
+      <c r="F11" s="1"/>
       <c r="G11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" t="s">
         <v>92</v>
       </c>
-      <c r="B12" t="s">
-        <v>93</v>
-      </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
         <v>59</v>
@@ -1895,276 +1905,290 @@
       <c r="E12" t="s">
         <v>58</v>
       </c>
+      <c r="F12" s="1"/>
       <c r="G12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" t="s">
         <v>94</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>95</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>96</v>
       </c>
-      <c r="D13" t="s">
-        <v>97</v>
-      </c>
       <c r="E13" t="s">
         <v>59</v>
       </c>
+      <c r="F13" s="1"/>
       <c r="G13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" t="s">
         <v>98</v>
-      </c>
-      <c r="B14" t="s">
-        <v>99</v>
       </c>
       <c r="C14" t="s">
         <v>57</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E14" t="s">
         <v>59</v>
       </c>
+      <c r="F14" s="1"/>
       <c r="G14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" t="s">
         <v>101</v>
-      </c>
-      <c r="B15" t="s">
-        <v>102</v>
       </c>
       <c r="C15" t="s">
         <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E15" t="s">
         <v>59</v>
       </c>
+      <c r="F15" s="1"/>
       <c r="G15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>102</v>
+      </c>
+      <c r="B16" t="s">
         <v>103</v>
       </c>
-      <c r="B16" t="s">
-        <v>104</v>
-      </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
         <v>59</v>
       </c>
       <c r="E16" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" t="s">
         <v>72</v>
-      </c>
-      <c r="G16" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" t="s">
         <v>105</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" t="s">
         <v>106</v>
       </c>
-      <c r="C17" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17" t="s">
-        <v>107</v>
-      </c>
       <c r="E17" t="s">
         <v>59</v>
       </c>
+      <c r="F17" s="1"/>
       <c r="G17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" t="s">
         <v>108</v>
       </c>
-      <c r="B18" t="s">
-        <v>109</v>
-      </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D18" t="s">
         <v>59</v>
       </c>
       <c r="E18" t="s">
-        <v>79</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="F18" s="1"/>
       <c r="G18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" t="s">
         <v>110</v>
       </c>
-      <c r="B19" t="s">
-        <v>111</v>
-      </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
         <v>59</v>
       </c>
       <c r="E19" t="s">
-        <v>88</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="F19" s="1"/>
       <c r="G19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>111</v>
+      </c>
+      <c r="B20" t="s">
         <v>112</v>
       </c>
-      <c r="B20" t="s">
-        <v>113</v>
-      </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E20" t="s">
         <v>59</v>
       </c>
+      <c r="F20" s="1"/>
       <c r="G20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B21" t="s">
         <v>114</v>
       </c>
-      <c r="B21" t="s">
-        <v>115</v>
-      </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
         <v>59</v>
       </c>
       <c r="E21" t="s">
-        <v>107</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="F21" s="1"/>
       <c r="G21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" t="s">
         <v>116</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>117</v>
       </c>
-      <c r="C22" t="s">
-        <v>118</v>
-      </c>
       <c r="D22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E22" t="s">
         <v>59</v>
       </c>
+      <c r="F22" s="1"/>
       <c r="G22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" t="s">
         <v>119</v>
       </c>
-      <c r="B23" t="s">
-        <v>120</v>
-      </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D23" t="s">
         <v>59</v>
       </c>
       <c r="E23" t="s">
-        <v>100</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="F23" s="1"/>
       <c r="G23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" t="s">
         <v>121</v>
-      </c>
-      <c r="B24" t="s">
-        <v>122</v>
       </c>
       <c r="C24" t="s">
         <v>57</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E24" t="s">
         <v>59</v>
       </c>
+      <c r="F24" s="1"/>
       <c r="G24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" t="s">
         <v>123</v>
       </c>
-      <c r="B25" t="s">
-        <v>124</v>
-      </c>
       <c r="C25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D25" t="s">
         <v>59</v>
       </c>
       <c r="E25" t="s">
-        <v>97</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="F25" s="1"/>
       <c r="G25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>124</v>
+      </c>
+      <c r="B26" t="s">
         <v>125</v>
-      </c>
-      <c r="B26" t="s">
-        <v>126</v>
       </c>
       <c r="C26" t="s">
         <v>57</v>
@@ -2175,8 +2199,9 @@
       <c r="E26" t="s">
         <v>59</v>
       </c>
+      <c r="F26" s="1"/>
       <c r="G26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2216,28 +2241,28 @@
         <v>0</v>
       </c>
       <c r="E1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G1" t="s">
         <v>127</v>
       </c>
-      <c r="F1" t="s">
-        <v>195</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>128</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>129</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>130</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>131</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>132</v>
-      </c>
-      <c r="L1" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -2257,7 +2282,7 @@
         <v>7</v>
       </c>
       <c r="G2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -2277,7 +2302,7 @@
         <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -2297,7 +2322,7 @@
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -2317,7 +2342,7 @@
         <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -2726,13 +2751,13 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B28" t="s">
         <v>59</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -2743,13 +2768,13 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B29" t="s">
         <v>59</v>
       </c>
       <c r="C29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D29">
         <v>2</v>
@@ -2760,13 +2785,13 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B30" t="s">
         <v>59</v>
       </c>
       <c r="C30" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D30">
         <v>3</v>
@@ -2777,13 +2802,13 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B31" t="s">
         <v>59</v>
       </c>
       <c r="C31" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D31">
         <v>4</v>
@@ -2794,13 +2819,13 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B32" t="s">
         <v>59</v>
       </c>
       <c r="C32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D32">
         <v>5</v>
@@ -2811,13 +2836,13 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B33" t="s">
         <v>59</v>
       </c>
       <c r="C33" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D33">
         <v>6</v>
@@ -2828,13 +2853,13 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B34" t="s">
         <v>59</v>
       </c>
       <c r="C34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D34">
         <v>7</v>
@@ -2845,13 +2870,13 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B35" t="s">
         <v>59</v>
       </c>
       <c r="C35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D35">
         <v>8</v>
@@ -2862,13 +2887,13 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B36" t="s">
         <v>59</v>
       </c>
       <c r="C36" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D36">
         <v>9</v>
@@ -2879,13 +2904,13 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B37" t="s">
         <v>59</v>
       </c>
       <c r="C37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D37">
         <v>10</v>
@@ -2896,13 +2921,13 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B38" t="s">
         <v>59</v>
       </c>
       <c r="C38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D38">
         <v>11</v>
@@ -2913,13 +2938,13 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B39" t="s">
         <v>59</v>
       </c>
       <c r="C39" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D39">
         <v>12</v>
@@ -2930,13 +2955,13 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B40" t="s">
         <v>59</v>
       </c>
       <c r="C40" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D40">
         <v>13</v>
@@ -2947,13 +2972,13 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B41" t="s">
         <v>59</v>
       </c>
       <c r="C41" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D41">
         <v>14</v>
@@ -2964,13 +2989,13 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B42" t="s">
         <v>59</v>
       </c>
       <c r="C42" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D42">
         <v>15</v>
@@ -2981,13 +3006,13 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B43" t="s">
         <v>59</v>
       </c>
       <c r="C43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D43">
         <v>16</v>
@@ -2998,13 +3023,13 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B44" t="s">
         <v>59</v>
       </c>
       <c r="C44" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D44">
         <v>17</v>
@@ -3015,13 +3040,13 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B45" t="s">
         <v>59</v>
       </c>
       <c r="C45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D45">
         <v>18</v>
@@ -3032,13 +3057,13 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B46" t="s">
         <v>59</v>
       </c>
       <c r="C46" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D46">
         <v>19</v>
@@ -3049,13 +3074,13 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B47" t="s">
         <v>59</v>
       </c>
       <c r="C47" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D47">
         <v>20</v>
@@ -3066,13 +3091,13 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B48" t="s">
         <v>59</v>
       </c>
       <c r="C48" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D48">
         <v>21</v>
@@ -3083,13 +3108,13 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B49" t="s">
         <v>59</v>
       </c>
       <c r="C49" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D49">
         <v>22</v>
@@ -3100,13 +3125,13 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B50" t="s">
         <v>59</v>
       </c>
       <c r="C50" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D50">
         <v>23</v>
@@ -3117,13 +3142,13 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B51" t="s">
         <v>59</v>
       </c>
       <c r="C51" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D51">
         <v>24</v>
@@ -3134,13 +3159,13 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B52" t="s">
         <v>59</v>
       </c>
       <c r="C52" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D52">
         <v>25</v>
@@ -3151,13 +3176,13 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B53" t="s">
         <v>59</v>
       </c>
       <c r="C53" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D53">
         <v>26</v>
@@ -3168,13 +3193,13 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B54" t="s">
         <v>59</v>
       </c>
       <c r="C54" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -3185,13 +3210,13 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B55" t="s">
         <v>59</v>
       </c>
       <c r="C55" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D55">
         <v>2</v>
@@ -3202,13 +3227,13 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B56" t="s">
         <v>59</v>
       </c>
       <c r="C56" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D56">
         <v>3</v>
@@ -3219,13 +3244,13 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B57" t="s">
         <v>59</v>
       </c>
       <c r="C57" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D57">
         <v>4</v>
@@ -3236,13 +3261,13 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B58" t="s">
         <v>59</v>
       </c>
       <c r="C58" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D58">
         <v>5</v>
@@ -3253,13 +3278,13 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B59" t="s">
         <v>59</v>
       </c>
       <c r="C59" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D59">
         <v>6</v>
@@ -3270,13 +3295,13 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B60" t="s">
         <v>59</v>
       </c>
       <c r="C60" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D60">
         <v>7</v>
@@ -3287,13 +3312,13 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B61" t="s">
         <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D61">
         <v>8</v>
@@ -3304,13 +3329,13 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B62" t="s">
         <v>59</v>
       </c>
       <c r="C62" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D62">
         <v>9</v>
@@ -3321,13 +3346,13 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" t="s">
         <v>59</v>
       </c>
       <c r="C63" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D63">
         <v>10</v>
@@ -3338,13 +3363,13 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B64" t="s">
         <v>59</v>
       </c>
       <c r="C64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D64">
         <v>11</v>
@@ -3355,13 +3380,13 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B65" t="s">
         <v>59</v>
       </c>
       <c r="C65" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D65">
         <v>12</v>
@@ -3372,13 +3397,13 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B66" t="s">
         <v>59</v>
       </c>
       <c r="C66" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D66">
         <v>13</v>
@@ -3389,13 +3414,13 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B67" t="s">
         <v>59</v>
       </c>
       <c r="C67" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D67">
         <v>14</v>
@@ -3406,13 +3431,13 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B68" t="s">
         <v>59</v>
       </c>
       <c r="C68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D68">
         <v>15</v>
@@ -3423,13 +3448,13 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B69" t="s">
         <v>59</v>
       </c>
       <c r="C69" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D69">
         <v>16</v>
@@ -3440,13 +3465,13 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B70" t="s">
         <v>59</v>
       </c>
       <c r="C70" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D70">
         <v>17</v>
@@ -3457,13 +3482,13 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B71" t="s">
         <v>59</v>
       </c>
       <c r="C71" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D71">
         <v>18</v>
@@ -3474,13 +3499,13 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B72" t="s">
         <v>59</v>
       </c>
       <c r="C72" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D72">
         <v>19</v>
@@ -3491,13 +3516,13 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B73" t="s">
         <v>59</v>
       </c>
       <c r="C73" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D73">
         <v>20</v>
@@ -3508,13 +3533,13 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B74" t="s">
         <v>59</v>
       </c>
       <c r="C74" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D74">
         <v>21</v>
@@ -3525,13 +3550,13 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B75" t="s">
         <v>59</v>
       </c>
       <c r="C75" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D75">
         <v>22</v>
@@ -3542,13 +3567,13 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B76" t="s">
         <v>59</v>
       </c>
       <c r="C76" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D76">
         <v>23</v>
@@ -3559,13 +3584,13 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B77" t="s">
         <v>59</v>
       </c>
       <c r="C77" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D77">
         <v>24</v>
@@ -3576,13 +3601,13 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B78" t="s">
         <v>59</v>
       </c>
       <c r="C78" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D78">
         <v>25</v>
@@ -3593,13 +3618,13 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B79" t="s">
         <v>59</v>
       </c>
       <c r="C79" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D79">
         <v>26</v>
@@ -3610,10 +3635,10 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B80" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C80" t="s">
         <v>59</v>
@@ -3627,10 +3652,10 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B81" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C81" t="s">
         <v>59</v>
@@ -3644,10 +3669,10 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B82" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C82" t="s">
         <v>59</v>
@@ -3661,10 +3686,10 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B83" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C83" t="s">
         <v>59</v>
@@ -3678,10 +3703,10 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B84" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C84" t="s">
         <v>59</v>
@@ -3695,10 +3720,10 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B85" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C85" t="s">
         <v>59</v>
@@ -3712,10 +3737,10 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B86" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C86" t="s">
         <v>59</v>
@@ -3729,10 +3754,10 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B87" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C87" t="s">
         <v>59</v>
@@ -3746,10 +3771,10 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B88" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C88" t="s">
         <v>59</v>
@@ -3763,10 +3788,10 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B89" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C89" t="s">
         <v>59</v>
@@ -3780,10 +3805,10 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B90" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C90" t="s">
         <v>59</v>
@@ -3797,10 +3822,10 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B91" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C91" t="s">
         <v>59</v>
@@ -3814,10 +3839,10 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B92" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C92" t="s">
         <v>59</v>
@@ -3831,10 +3856,10 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B93" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C93" t="s">
         <v>59</v>
@@ -3848,10 +3873,10 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B94" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C94" t="s">
         <v>59</v>
@@ -3865,10 +3890,10 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B95" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C95" t="s">
         <v>59</v>
@@ -3882,10 +3907,10 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B96" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C96" t="s">
         <v>59</v>
@@ -3899,10 +3924,10 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B97" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C97" t="s">
         <v>59</v>
@@ -3916,10 +3941,10 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B98" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C98" t="s">
         <v>59</v>
@@ -3933,10 +3958,10 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B99" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C99" t="s">
         <v>59</v>
@@ -3950,10 +3975,10 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B100" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C100" t="s">
         <v>59</v>
@@ -3967,10 +3992,10 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B101" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C101" t="s">
         <v>59</v>
@@ -3984,10 +4009,10 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B102" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C102" t="s">
         <v>59</v>
@@ -4001,10 +4026,10 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B103" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C103" t="s">
         <v>59</v>
@@ -4018,10 +4043,10 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B104" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C104" t="s">
         <v>59</v>
@@ -4035,10 +4060,10 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B105" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C105" t="s">
         <v>59</v>
@@ -4052,13 +4077,13 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B106" t="s">
         <v>59</v>
       </c>
       <c r="C106" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -4069,13 +4094,13 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B107" t="s">
         <v>59</v>
       </c>
       <c r="C107" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D107">
         <v>2</v>
@@ -4086,13 +4111,13 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B108" t="s">
         <v>59</v>
       </c>
       <c r="C108" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D108">
         <v>3</v>
@@ -4103,13 +4128,13 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B109" t="s">
         <v>59</v>
       </c>
       <c r="C109" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D109">
         <v>4</v>
@@ -4120,13 +4145,13 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B110" t="s">
         <v>59</v>
       </c>
       <c r="C110" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D110">
         <v>5</v>
@@ -4137,13 +4162,13 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B111" t="s">
         <v>59</v>
       </c>
       <c r="C111" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D111">
         <v>6</v>
@@ -4154,13 +4179,13 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B112" t="s">
         <v>59</v>
       </c>
       <c r="C112" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D112">
         <v>7</v>
@@ -4171,13 +4196,13 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B113" t="s">
         <v>59</v>
       </c>
       <c r="C113" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D113">
         <v>8</v>
@@ -4188,13 +4213,13 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B114" t="s">
         <v>59</v>
       </c>
       <c r="C114" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D114">
         <v>9</v>
@@ -4205,13 +4230,13 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B115" t="s">
         <v>59</v>
       </c>
       <c r="C115" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D115">
         <v>10</v>
@@ -4222,13 +4247,13 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B116" t="s">
         <v>59</v>
       </c>
       <c r="C116" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D116">
         <v>11</v>
@@ -4239,13 +4264,13 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B117" t="s">
         <v>59</v>
       </c>
       <c r="C117" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D117">
         <v>12</v>
@@ -4256,13 +4281,13 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B118" t="s">
         <v>59</v>
       </c>
       <c r="C118" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D118">
         <v>13</v>
@@ -4273,13 +4298,13 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B119" t="s">
         <v>59</v>
       </c>
       <c r="C119" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D119">
         <v>14</v>
@@ -4290,13 +4315,13 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B120" t="s">
         <v>59</v>
       </c>
       <c r="C120" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D120">
         <v>15</v>
@@ -4307,13 +4332,13 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B121" t="s">
         <v>59</v>
       </c>
       <c r="C121" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D121">
         <v>16</v>
@@ -4324,13 +4349,13 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B122" t="s">
         <v>59</v>
       </c>
       <c r="C122" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D122">
         <v>17</v>
@@ -4341,13 +4366,13 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B123" t="s">
         <v>59</v>
       </c>
       <c r="C123" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D123">
         <v>18</v>
@@ -4358,13 +4383,13 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B124" t="s">
         <v>59</v>
       </c>
       <c r="C124" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D124">
         <v>19</v>
@@ -4375,13 +4400,13 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B125" t="s">
         <v>59</v>
       </c>
       <c r="C125" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D125">
         <v>20</v>
@@ -4392,13 +4417,13 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B126" t="s">
         <v>59</v>
       </c>
       <c r="C126" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D126">
         <v>21</v>
@@ -4409,13 +4434,13 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B127" t="s">
         <v>59</v>
       </c>
       <c r="C127" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D127">
         <v>22</v>
@@ -4426,13 +4451,13 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B128" t="s">
         <v>59</v>
       </c>
       <c r="C128" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D128">
         <v>23</v>
@@ -4443,13 +4468,13 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B129" t="s">
         <v>59</v>
       </c>
       <c r="C129" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D129">
         <v>24</v>
@@ -4460,13 +4485,13 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B130" t="s">
         <v>59</v>
       </c>
       <c r="C130" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D130">
         <v>25</v>
@@ -4477,13 +4502,13 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B131" t="s">
         <v>59</v>
       </c>
       <c r="C131" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D131">
         <v>26</v>
@@ -4494,10 +4519,10 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B132" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C132" t="s">
         <v>59</v>
@@ -4511,10 +4536,10 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B133" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C133" t="s">
         <v>59</v>
@@ -4528,10 +4553,10 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B134" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C134" t="s">
         <v>59</v>
@@ -4545,10 +4570,10 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B135" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C135" t="s">
         <v>59</v>
@@ -4562,10 +4587,10 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B136" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C136" t="s">
         <v>59</v>
@@ -4579,10 +4604,10 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B137" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C137" t="s">
         <v>59</v>
@@ -4596,10 +4621,10 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B138" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C138" t="s">
         <v>59</v>
@@ -4613,10 +4638,10 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B139" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C139" t="s">
         <v>59</v>
@@ -4630,10 +4655,10 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B140" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C140" t="s">
         <v>59</v>
@@ -4647,10 +4672,10 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B141" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C141" t="s">
         <v>59</v>
@@ -4664,10 +4689,10 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B142" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C142" t="s">
         <v>59</v>
@@ -4681,10 +4706,10 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B143" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C143" t="s">
         <v>59</v>
@@ -4698,10 +4723,10 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B144" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C144" t="s">
         <v>59</v>
@@ -4715,10 +4740,10 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B145" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C145" t="s">
         <v>59</v>
@@ -4732,10 +4757,10 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B146" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C146" t="s">
         <v>59</v>
@@ -4749,10 +4774,10 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B147" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C147" t="s">
         <v>59</v>
@@ -4766,10 +4791,10 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B148" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C148" t="s">
         <v>59</v>
@@ -4783,10 +4808,10 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B149" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C149" t="s">
         <v>59</v>
@@ -4800,10 +4825,10 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B150" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C150" t="s">
         <v>59</v>
@@ -4817,10 +4842,10 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B151" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C151" t="s">
         <v>59</v>
@@ -4834,10 +4859,10 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B152" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C152" t="s">
         <v>59</v>
@@ -4851,10 +4876,10 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B153" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C153" t="s">
         <v>59</v>
@@ -4868,10 +4893,10 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B154" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C154" t="s">
         <v>59</v>
@@ -4885,10 +4910,10 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B155" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C155" t="s">
         <v>59</v>
@@ -4902,10 +4927,10 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B156" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C156" t="s">
         <v>59</v>
@@ -4919,10 +4944,10 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B157" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C157" t="s">
         <v>59</v>
@@ -4936,13 +4961,13 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B158" t="s">
         <v>59</v>
       </c>
       <c r="C158" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D158">
         <v>1</v>
@@ -4953,13 +4978,13 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B159" t="s">
         <v>59</v>
       </c>
       <c r="C159" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D159">
         <v>2</v>
@@ -4970,13 +4995,13 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B160" t="s">
         <v>59</v>
       </c>
       <c r="C160" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D160">
         <v>3</v>
@@ -4987,13 +5012,13 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B161" t="s">
         <v>59</v>
       </c>
       <c r="C161" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D161">
         <v>4</v>
@@ -5004,13 +5029,13 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B162" t="s">
         <v>59</v>
       </c>
       <c r="C162" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D162">
         <v>5</v>
@@ -5021,13 +5046,13 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B163" t="s">
         <v>59</v>
       </c>
       <c r="C163" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D163">
         <v>6</v>
@@ -5038,13 +5063,13 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B164" t="s">
         <v>59</v>
       </c>
       <c r="C164" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D164">
         <v>7</v>
@@ -5055,13 +5080,13 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B165" t="s">
         <v>59</v>
       </c>
       <c r="C165" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D165">
         <v>8</v>
@@ -5072,13 +5097,13 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B166" t="s">
         <v>59</v>
       </c>
       <c r="C166" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D166">
         <v>9</v>
@@ -5089,13 +5114,13 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B167" t="s">
         <v>59</v>
       </c>
       <c r="C167" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D167">
         <v>10</v>
@@ -5106,13 +5131,13 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B168" t="s">
         <v>59</v>
       </c>
       <c r="C168" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D168">
         <v>11</v>
@@ -5123,13 +5148,13 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B169" t="s">
         <v>59</v>
       </c>
       <c r="C169" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D169">
         <v>12</v>
@@ -5140,13 +5165,13 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B170" t="s">
         <v>59</v>
       </c>
       <c r="C170" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D170">
         <v>13</v>
@@ -5157,13 +5182,13 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B171" t="s">
         <v>59</v>
       </c>
       <c r="C171" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D171">
         <v>14</v>
@@ -5174,13 +5199,13 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B172" t="s">
         <v>59</v>
       </c>
       <c r="C172" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D172">
         <v>15</v>
@@ -5191,13 +5216,13 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B173" t="s">
         <v>59</v>
       </c>
       <c r="C173" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D173">
         <v>16</v>
@@ -5208,13 +5233,13 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B174" t="s">
         <v>59</v>
       </c>
       <c r="C174" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D174">
         <v>17</v>
@@ -5225,13 +5250,13 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B175" t="s">
         <v>59</v>
       </c>
       <c r="C175" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D175">
         <v>18</v>
@@ -5242,13 +5267,13 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B176" t="s">
         <v>59</v>
       </c>
       <c r="C176" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D176">
         <v>19</v>
@@ -5259,13 +5284,13 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B177" t="s">
         <v>59</v>
       </c>
       <c r="C177" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D177">
         <v>20</v>
@@ -5276,13 +5301,13 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B178" t="s">
         <v>59</v>
       </c>
       <c r="C178" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D178">
         <v>21</v>
@@ -5293,13 +5318,13 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B179" t="s">
         <v>59</v>
       </c>
       <c r="C179" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D179">
         <v>22</v>
@@ -5310,13 +5335,13 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B180" t="s">
         <v>59</v>
       </c>
       <c r="C180" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D180">
         <v>23</v>
@@ -5327,13 +5352,13 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B181" t="s">
         <v>59</v>
       </c>
       <c r="C181" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D181">
         <v>24</v>
@@ -5344,13 +5369,13 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B182" t="s">
         <v>59</v>
       </c>
       <c r="C182" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D182">
         <v>25</v>
@@ -5361,13 +5386,13 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B183" t="s">
         <v>59</v>
       </c>
       <c r="C183" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D183">
         <v>26</v>
@@ -5378,13 +5403,13 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B184" t="s">
         <v>59</v>
       </c>
       <c r="C184" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D184">
         <v>1</v>
@@ -5395,13 +5420,13 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B185" t="s">
         <v>59</v>
       </c>
       <c r="C185" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D185">
         <v>2</v>
@@ -5412,13 +5437,13 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B186" t="s">
         <v>59</v>
       </c>
       <c r="C186" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D186">
         <v>3</v>
@@ -5429,13 +5454,13 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B187" t="s">
         <v>59</v>
       </c>
       <c r="C187" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D187">
         <v>4</v>
@@ -5446,13 +5471,13 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B188" t="s">
         <v>59</v>
       </c>
       <c r="C188" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D188">
         <v>5</v>
@@ -5463,13 +5488,13 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B189" t="s">
         <v>59</v>
       </c>
       <c r="C189" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D189">
         <v>6</v>
@@ -5480,13 +5505,13 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B190" t="s">
         <v>59</v>
       </c>
       <c r="C190" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D190">
         <v>7</v>
@@ -5497,13 +5522,13 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B191" t="s">
         <v>59</v>
       </c>
       <c r="C191" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D191">
         <v>8</v>
@@ -5514,13 +5539,13 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B192" t="s">
         <v>59</v>
       </c>
       <c r="C192" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D192">
         <v>9</v>
@@ -5531,13 +5556,13 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B193" t="s">
         <v>59</v>
       </c>
       <c r="C193" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D193">
         <v>10</v>
@@ -5548,13 +5573,13 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B194" t="s">
         <v>59</v>
       </c>
       <c r="C194" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D194">
         <v>11</v>
@@ -5565,13 +5590,13 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B195" t="s">
         <v>59</v>
       </c>
       <c r="C195" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D195">
         <v>12</v>
@@ -5582,13 +5607,13 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B196" t="s">
         <v>59</v>
       </c>
       <c r="C196" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D196">
         <v>13</v>
@@ -5599,13 +5624,13 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B197" t="s">
         <v>59</v>
       </c>
       <c r="C197" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D197">
         <v>14</v>
@@ -5616,13 +5641,13 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B198" t="s">
         <v>59</v>
       </c>
       <c r="C198" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D198">
         <v>15</v>
@@ -5633,13 +5658,13 @@
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B199" t="s">
         <v>59</v>
       </c>
       <c r="C199" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D199">
         <v>16</v>
@@ -5650,13 +5675,13 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B200" t="s">
         <v>59</v>
       </c>
       <c r="C200" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D200">
         <v>17</v>
@@ -5667,13 +5692,13 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B201" t="s">
         <v>59</v>
       </c>
       <c r="C201" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D201">
         <v>18</v>
@@ -5684,13 +5709,13 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B202" t="s">
         <v>59</v>
       </c>
       <c r="C202" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D202">
         <v>19</v>
@@ -5701,13 +5726,13 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B203" t="s">
         <v>59</v>
       </c>
       <c r="C203" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D203">
         <v>20</v>
@@ -5718,13 +5743,13 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B204" t="s">
         <v>59</v>
       </c>
       <c r="C204" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D204">
         <v>21</v>
@@ -5735,13 +5760,13 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B205" t="s">
         <v>59</v>
       </c>
       <c r="C205" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D205">
         <v>22</v>
@@ -5752,13 +5777,13 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B206" t="s">
         <v>59</v>
       </c>
       <c r="C206" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D206">
         <v>23</v>
@@ -5769,13 +5794,13 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B207" t="s">
         <v>59</v>
       </c>
       <c r="C207" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D207">
         <v>24</v>
@@ -5786,13 +5811,13 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B208" t="s">
         <v>59</v>
       </c>
       <c r="C208" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D208">
         <v>25</v>
@@ -5803,13 +5828,13 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B209" t="s">
         <v>59</v>
       </c>
       <c r="C209" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D209">
         <v>26</v>
@@ -5820,10 +5845,10 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B210" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C210" t="s">
         <v>59</v>
@@ -5837,10 +5862,10 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B211" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C211" t="s">
         <v>59</v>
@@ -5854,10 +5879,10 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B212" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C212" t="s">
         <v>59</v>
@@ -5871,10 +5896,10 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B213" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C213" t="s">
         <v>59</v>
@@ -5888,10 +5913,10 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B214" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C214" t="s">
         <v>59</v>
@@ -5905,10 +5930,10 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B215" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C215" t="s">
         <v>59</v>
@@ -5922,10 +5947,10 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B216" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C216" t="s">
         <v>59</v>
@@ -5939,10 +5964,10 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B217" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C217" t="s">
         <v>59</v>
@@ -5956,10 +5981,10 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B218" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C218" t="s">
         <v>59</v>
@@ -5973,10 +5998,10 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B219" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C219" t="s">
         <v>59</v>
@@ -5990,10 +6015,10 @@
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B220" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C220" t="s">
         <v>59</v>
@@ -6007,10 +6032,10 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B221" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C221" t="s">
         <v>59</v>
@@ -6024,10 +6049,10 @@
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B222" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C222" t="s">
         <v>59</v>
@@ -6041,10 +6066,10 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B223" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C223" t="s">
         <v>59</v>
@@ -6058,10 +6083,10 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B224" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C224" t="s">
         <v>59</v>
@@ -6075,10 +6100,10 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B225" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C225" t="s">
         <v>59</v>
@@ -6092,10 +6117,10 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B226" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C226" t="s">
         <v>59</v>
@@ -6109,10 +6134,10 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B227" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C227" t="s">
         <v>59</v>
@@ -6126,10 +6151,10 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B228" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C228" t="s">
         <v>59</v>
@@ -6143,10 +6168,10 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B229" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C229" t="s">
         <v>59</v>
@@ -6160,10 +6185,10 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B230" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C230" t="s">
         <v>59</v>
@@ -6177,10 +6202,10 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B231" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C231" t="s">
         <v>59</v>
@@ -6194,10 +6219,10 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B232" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C232" t="s">
         <v>59</v>
@@ -6211,10 +6236,10 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B233" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C233" t="s">
         <v>59</v>
@@ -6228,10 +6253,10 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B234" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C234" t="s">
         <v>59</v>
@@ -6245,10 +6270,10 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B235" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C235" t="s">
         <v>59</v>
@@ -6262,13 +6287,13 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B236" t="s">
         <v>59</v>
       </c>
       <c r="C236" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D236">
         <v>1</v>
@@ -6279,13 +6304,13 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B237" t="s">
         <v>59</v>
       </c>
       <c r="C237" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D237">
         <v>2</v>
@@ -6296,13 +6321,13 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B238" t="s">
         <v>59</v>
       </c>
       <c r="C238" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D238">
         <v>3</v>
@@ -6313,13 +6338,13 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B239" t="s">
         <v>59</v>
       </c>
       <c r="C239" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D239">
         <v>4</v>
@@ -6330,13 +6355,13 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B240" t="s">
         <v>59</v>
       </c>
       <c r="C240" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D240">
         <v>5</v>
@@ -6347,13 +6372,13 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B241" t="s">
         <v>59</v>
       </c>
       <c r="C241" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D241">
         <v>6</v>
@@ -6364,13 +6389,13 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B242" t="s">
         <v>59</v>
       </c>
       <c r="C242" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D242">
         <v>7</v>
@@ -6381,13 +6406,13 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B243" t="s">
         <v>59</v>
       </c>
       <c r="C243" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D243">
         <v>8</v>
@@ -6398,13 +6423,13 @@
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B244" t="s">
         <v>59</v>
       </c>
       <c r="C244" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D244">
         <v>9</v>
@@ -6415,13 +6440,13 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B245" t="s">
         <v>59</v>
       </c>
       <c r="C245" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D245">
         <v>10</v>
@@ -6432,13 +6457,13 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B246" t="s">
         <v>59</v>
       </c>
       <c r="C246" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D246">
         <v>11</v>
@@ -6449,13 +6474,13 @@
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B247" t="s">
         <v>59</v>
       </c>
       <c r="C247" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D247">
         <v>12</v>
@@ -6466,13 +6491,13 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B248" t="s">
         <v>59</v>
       </c>
       <c r="C248" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D248">
         <v>13</v>
@@ -6483,13 +6508,13 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B249" t="s">
         <v>59</v>
       </c>
       <c r="C249" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D249">
         <v>14</v>
@@ -6500,13 +6525,13 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B250" t="s">
         <v>59</v>
       </c>
       <c r="C250" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D250">
         <v>15</v>
@@ -6517,13 +6542,13 @@
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B251" t="s">
         <v>59</v>
       </c>
       <c r="C251" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D251">
         <v>16</v>
@@ -6534,13 +6559,13 @@
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B252" t="s">
         <v>59</v>
       </c>
       <c r="C252" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D252">
         <v>17</v>
@@ -6551,13 +6576,13 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B253" t="s">
         <v>59</v>
       </c>
       <c r="C253" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D253">
         <v>18</v>
@@ -6568,13 +6593,13 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B254" t="s">
         <v>59</v>
       </c>
       <c r="C254" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D254">
         <v>19</v>
@@ -6585,13 +6610,13 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B255" t="s">
         <v>59</v>
       </c>
       <c r="C255" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D255">
         <v>20</v>
@@ -6602,13 +6627,13 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B256" t="s">
         <v>59</v>
       </c>
       <c r="C256" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D256">
         <v>21</v>
@@ -6619,13 +6644,13 @@
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B257" t="s">
         <v>59</v>
       </c>
       <c r="C257" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D257">
         <v>22</v>
@@ -6636,13 +6661,13 @@
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B258" t="s">
         <v>59</v>
       </c>
       <c r="C258" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D258">
         <v>23</v>
@@ -6653,13 +6678,13 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B259" t="s">
         <v>59</v>
       </c>
       <c r="C259" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D259">
         <v>24</v>
@@ -6670,13 +6695,13 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B260" t="s">
         <v>59</v>
       </c>
       <c r="C260" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D260">
         <v>25</v>
@@ -6687,13 +6712,13 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B261" t="s">
         <v>59</v>
       </c>
       <c r="C261" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D261">
         <v>26</v>
@@ -6704,7 +6729,7 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B262" t="s">
         <v>59</v>
@@ -6721,7 +6746,7 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B263" t="s">
         <v>59</v>
@@ -6738,7 +6763,7 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B264" t="s">
         <v>59</v>
@@ -6755,7 +6780,7 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B265" t="s">
         <v>59</v>
@@ -6772,7 +6797,7 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B266" t="s">
         <v>59</v>
@@ -6789,7 +6814,7 @@
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B267" t="s">
         <v>59</v>
@@ -6806,7 +6831,7 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B268" t="s">
         <v>59</v>
@@ -6823,7 +6848,7 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B269" t="s">
         <v>59</v>
@@ -6840,7 +6865,7 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B270" t="s">
         <v>59</v>
@@ -6857,7 +6882,7 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B271" t="s">
         <v>59</v>
@@ -6874,7 +6899,7 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B272" t="s">
         <v>59</v>
@@ -6891,7 +6916,7 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B273" t="s">
         <v>59</v>
@@ -6908,7 +6933,7 @@
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B274" t="s">
         <v>59</v>
@@ -6925,7 +6950,7 @@
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B275" t="s">
         <v>59</v>
@@ -6942,7 +6967,7 @@
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B276" t="s">
         <v>59</v>
@@ -6959,7 +6984,7 @@
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B277" t="s">
         <v>59</v>
@@ -6976,7 +7001,7 @@
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B278" t="s">
         <v>59</v>
@@ -6993,7 +7018,7 @@
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B279" t="s">
         <v>59</v>
@@ -7010,7 +7035,7 @@
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B280" t="s">
         <v>59</v>
@@ -7027,7 +7052,7 @@
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B281" t="s">
         <v>59</v>
@@ -7044,7 +7069,7 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B282" t="s">
         <v>59</v>
@@ -7061,7 +7086,7 @@
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B283" t="s">
         <v>59</v>
@@ -7078,7 +7103,7 @@
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B284" t="s">
         <v>59</v>
@@ -7095,7 +7120,7 @@
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B285" t="s">
         <v>59</v>
@@ -7112,7 +7137,7 @@
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B286" t="s">
         <v>59</v>
@@ -7129,7 +7154,7 @@
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B287" t="s">
         <v>59</v>
@@ -7146,10 +7171,10 @@
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B288" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C288" t="s">
         <v>59</v>
@@ -7163,10 +7188,10 @@
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B289" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C289" t="s">
         <v>59</v>
@@ -7180,10 +7205,10 @@
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B290" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C290" t="s">
         <v>59</v>
@@ -7197,10 +7222,10 @@
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B291" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C291" t="s">
         <v>59</v>
@@ -7214,10 +7239,10 @@
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B292" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C292" t="s">
         <v>59</v>
@@ -7231,10 +7256,10 @@
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B293" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C293" t="s">
         <v>59</v>
@@ -7248,10 +7273,10 @@
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B294" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C294" t="s">
         <v>59</v>
@@ -7265,10 +7290,10 @@
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B295" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C295" t="s">
         <v>59</v>
@@ -7282,10 +7307,10 @@
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B296" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C296" t="s">
         <v>59</v>
@@ -7299,10 +7324,10 @@
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B297" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C297" t="s">
         <v>59</v>
@@ -7316,10 +7341,10 @@
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B298" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C298" t="s">
         <v>59</v>
@@ -7333,10 +7358,10 @@
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B299" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C299" t="s">
         <v>59</v>
@@ -7350,10 +7375,10 @@
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B300" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C300" t="s">
         <v>59</v>
@@ -7367,10 +7392,10 @@
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B301" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C301" t="s">
         <v>59</v>
@@ -7384,10 +7409,10 @@
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B302" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C302" t="s">
         <v>59</v>
@@ -7401,10 +7426,10 @@
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B303" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C303" t="s">
         <v>59</v>
@@ -7418,10 +7443,10 @@
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B304" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C304" t="s">
         <v>59</v>
@@ -7435,10 +7460,10 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B305" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C305" t="s">
         <v>59</v>
@@ -7452,10 +7477,10 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B306" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C306" t="s">
         <v>59</v>
@@ -7469,10 +7494,10 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B307" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C307" t="s">
         <v>59</v>
@@ -7486,10 +7511,10 @@
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B308" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C308" t="s">
         <v>59</v>
@@ -7503,10 +7528,10 @@
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B309" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C309" t="s">
         <v>59</v>
@@ -7520,10 +7545,10 @@
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B310" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C310" t="s">
         <v>59</v>
@@ -7537,10 +7562,10 @@
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B311" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C311" t="s">
         <v>59</v>
@@ -7554,10 +7579,10 @@
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B312" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C312" t="s">
         <v>59</v>
@@ -7571,10 +7596,10 @@
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B313" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C313" t="s">
         <v>59</v>
@@ -7588,10 +7613,10 @@
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B314" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C314" t="s">
         <v>59</v>
@@ -7605,10 +7630,10 @@
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B315" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C315" t="s">
         <v>59</v>
@@ -7622,10 +7647,10 @@
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B316" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C316" t="s">
         <v>59</v>
@@ -7639,10 +7664,10 @@
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B317" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C317" t="s">
         <v>59</v>
@@ -7656,10 +7681,10 @@
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B318" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C318" t="s">
         <v>59</v>
@@ -7673,10 +7698,10 @@
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B319" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C319" t="s">
         <v>59</v>
@@ -7690,10 +7715,10 @@
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B320" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C320" t="s">
         <v>59</v>
@@ -7707,10 +7732,10 @@
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B321" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C321" t="s">
         <v>59</v>
@@ -7724,10 +7749,10 @@
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B322" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C322" t="s">
         <v>59</v>
@@ -7741,10 +7766,10 @@
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B323" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C323" t="s">
         <v>59</v>
@@ -7758,10 +7783,10 @@
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B324" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C324" t="s">
         <v>59</v>
@@ -7775,10 +7800,10 @@
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B325" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C325" t="s">
         <v>59</v>
@@ -7792,10 +7817,10 @@
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B326" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C326" t="s">
         <v>59</v>
@@ -7809,10 +7834,10 @@
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B327" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C327" t="s">
         <v>59</v>
@@ -7826,10 +7851,10 @@
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B328" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C328" t="s">
         <v>59</v>
@@ -7843,10 +7868,10 @@
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B329" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C329" t="s">
         <v>59</v>
@@ -7860,10 +7885,10 @@
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B330" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C330" t="s">
         <v>59</v>
@@ -7877,10 +7902,10 @@
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B331" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C331" t="s">
         <v>59</v>
@@ -7894,10 +7919,10 @@
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B332" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C332" t="s">
         <v>59</v>
@@ -7911,10 +7936,10 @@
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B333" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C333" t="s">
         <v>59</v>
@@ -7928,10 +7953,10 @@
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B334" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C334" t="s">
         <v>59</v>
@@ -7945,10 +7970,10 @@
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B335" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C335" t="s">
         <v>59</v>
@@ -7962,10 +7987,10 @@
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B336" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C336" t="s">
         <v>59</v>
@@ -7979,10 +8004,10 @@
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B337" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C337" t="s">
         <v>59</v>
@@ -7996,10 +8021,10 @@
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B338" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C338" t="s">
         <v>59</v>
@@ -8013,10 +8038,10 @@
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B339" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C339" t="s">
         <v>59</v>
@@ -8030,10 +8055,10 @@
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B340" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C340" t="s">
         <v>59</v>
@@ -8047,10 +8072,10 @@
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B341" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C341" t="s">
         <v>59</v>
@@ -8064,10 +8089,10 @@
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B342" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C342" t="s">
         <v>59</v>
@@ -8081,10 +8106,10 @@
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B343" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C343" t="s">
         <v>59</v>
@@ -8098,10 +8123,10 @@
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B344" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C344" t="s">
         <v>59</v>
@@ -8115,10 +8140,10 @@
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B345" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C345" t="s">
         <v>59</v>
@@ -8132,10 +8157,10 @@
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B346" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C346" t="s">
         <v>59</v>
@@ -8149,10 +8174,10 @@
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B347" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C347" t="s">
         <v>59</v>
@@ -8166,10 +8191,10 @@
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B348" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C348" t="s">
         <v>59</v>
@@ -8183,10 +8208,10 @@
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B349" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C349" t="s">
         <v>59</v>
@@ -8200,10 +8225,10 @@
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B350" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C350" t="s">
         <v>59</v>
@@ -8217,10 +8242,10 @@
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B351" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C351" t="s">
         <v>59</v>
@@ -8234,10 +8259,10 @@
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B352" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C352" t="s">
         <v>59</v>
@@ -8251,10 +8276,10 @@
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B353" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C353" t="s">
         <v>59</v>
@@ -8268,10 +8293,10 @@
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B354" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C354" t="s">
         <v>59</v>
@@ -8285,10 +8310,10 @@
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B355" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C355" t="s">
         <v>59</v>
@@ -8302,10 +8327,10 @@
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B356" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C356" t="s">
         <v>59</v>
@@ -8319,10 +8344,10 @@
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B357" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C357" t="s">
         <v>59</v>
@@ -8336,10 +8361,10 @@
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B358" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C358" t="s">
         <v>59</v>
@@ -8353,10 +8378,10 @@
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B359" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C359" t="s">
         <v>59</v>
@@ -8370,10 +8395,10 @@
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B360" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C360" t="s">
         <v>59</v>
@@ -8387,10 +8412,10 @@
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B361" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C361" t="s">
         <v>59</v>
@@ -8404,10 +8429,10 @@
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B362" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C362" t="s">
         <v>59</v>
@@ -8421,10 +8446,10 @@
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B363" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C363" t="s">
         <v>59</v>
@@ -8438,10 +8463,10 @@
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B364" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C364" t="s">
         <v>59</v>
@@ -8455,10 +8480,10 @@
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B365" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C365" t="s">
         <v>59</v>
@@ -8472,13 +8497,13 @@
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B366" t="s">
         <v>59</v>
       </c>
       <c r="C366" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D366">
         <v>1</v>
@@ -8489,13 +8514,13 @@
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B367" t="s">
         <v>59</v>
       </c>
       <c r="C367" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D367">
         <v>2</v>
@@ -8506,13 +8531,13 @@
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B368" t="s">
         <v>59</v>
       </c>
       <c r="C368" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D368">
         <v>3</v>
@@ -8523,13 +8548,13 @@
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B369" t="s">
         <v>59</v>
       </c>
       <c r="C369" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D369">
         <v>4</v>
@@ -8540,13 +8565,13 @@
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B370" t="s">
         <v>59</v>
       </c>
       <c r="C370" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D370">
         <v>5</v>
@@ -8557,13 +8582,13 @@
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B371" t="s">
         <v>59</v>
       </c>
       <c r="C371" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D371">
         <v>6</v>
@@ -8574,13 +8599,13 @@
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B372" t="s">
         <v>59</v>
       </c>
       <c r="C372" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D372">
         <v>7</v>
@@ -8591,13 +8616,13 @@
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B373" t="s">
         <v>59</v>
       </c>
       <c r="C373" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D373">
         <v>8</v>
@@ -8608,13 +8633,13 @@
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B374" t="s">
         <v>59</v>
       </c>
       <c r="C374" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D374">
         <v>9</v>
@@ -8625,13 +8650,13 @@
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B375" t="s">
         <v>59</v>
       </c>
       <c r="C375" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D375">
         <v>10</v>
@@ -8642,13 +8667,13 @@
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B376" t="s">
         <v>59</v>
       </c>
       <c r="C376" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D376">
         <v>11</v>
@@ -8659,13 +8684,13 @@
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B377" t="s">
         <v>59</v>
       </c>
       <c r="C377" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D377">
         <v>12</v>
@@ -8676,13 +8701,13 @@
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B378" t="s">
         <v>59</v>
       </c>
       <c r="C378" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D378">
         <v>13</v>
@@ -8693,13 +8718,13 @@
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B379" t="s">
         <v>59</v>
       </c>
       <c r="C379" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D379">
         <v>14</v>
@@ -8710,13 +8735,13 @@
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B380" t="s">
         <v>59</v>
       </c>
       <c r="C380" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D380">
         <v>15</v>
@@ -8727,13 +8752,13 @@
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B381" t="s">
         <v>59</v>
       </c>
       <c r="C381" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D381">
         <v>16</v>
@@ -8744,13 +8769,13 @@
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B382" t="s">
         <v>59</v>
       </c>
       <c r="C382" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D382">
         <v>17</v>
@@ -8761,13 +8786,13 @@
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B383" t="s">
         <v>59</v>
       </c>
       <c r="C383" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D383">
         <v>18</v>
@@ -8778,13 +8803,13 @@
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B384" t="s">
         <v>59</v>
       </c>
       <c r="C384" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D384">
         <v>19</v>
@@ -8795,13 +8820,13 @@
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B385" t="s">
         <v>59</v>
       </c>
       <c r="C385" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D385">
         <v>20</v>
@@ -8812,13 +8837,13 @@
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B386" t="s">
         <v>59</v>
       </c>
       <c r="C386" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D386">
         <v>21</v>
@@ -8829,13 +8854,13 @@
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B387" t="s">
         <v>59</v>
       </c>
       <c r="C387" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D387">
         <v>22</v>
@@ -8846,13 +8871,13 @@
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B388" t="s">
         <v>59</v>
       </c>
       <c r="C388" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D388">
         <v>23</v>
@@ -8863,13 +8888,13 @@
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B389" t="s">
         <v>59</v>
       </c>
       <c r="C389" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D389">
         <v>24</v>
@@ -8880,13 +8905,13 @@
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B390" t="s">
         <v>59</v>
       </c>
       <c r="C390" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D390">
         <v>25</v>
@@ -8897,13 +8922,13 @@
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B391" t="s">
         <v>59</v>
       </c>
       <c r="C391" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D391">
         <v>26</v>
@@ -8914,10 +8939,10 @@
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B392" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C392" t="s">
         <v>59</v>
@@ -8931,10 +8956,10 @@
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B393" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C393" t="s">
         <v>59</v>
@@ -8948,10 +8973,10 @@
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B394" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C394" t="s">
         <v>59</v>
@@ -8965,10 +8990,10 @@
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B395" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C395" t="s">
         <v>59</v>
@@ -8982,10 +9007,10 @@
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B396" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C396" t="s">
         <v>59</v>
@@ -8999,10 +9024,10 @@
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B397" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C397" t="s">
         <v>59</v>
@@ -9016,10 +9041,10 @@
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B398" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C398" t="s">
         <v>59</v>
@@ -9033,10 +9058,10 @@
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B399" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C399" t="s">
         <v>59</v>
@@ -9050,10 +9075,10 @@
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B400" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C400" t="s">
         <v>59</v>
@@ -9067,10 +9092,10 @@
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B401" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C401" t="s">
         <v>59</v>
@@ -9084,10 +9109,10 @@
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B402" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C402" t="s">
         <v>59</v>
@@ -9101,10 +9126,10 @@
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B403" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C403" t="s">
         <v>59</v>
@@ -9118,10 +9143,10 @@
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B404" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C404" t="s">
         <v>59</v>
@@ -9135,10 +9160,10 @@
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B405" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C405" t="s">
         <v>59</v>
@@ -9152,10 +9177,10 @@
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B406" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C406" t="s">
         <v>59</v>
@@ -9169,10 +9194,10 @@
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B407" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C407" t="s">
         <v>59</v>
@@ -9186,10 +9211,10 @@
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B408" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C408" t="s">
         <v>59</v>
@@ -9203,10 +9228,10 @@
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B409" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C409" t="s">
         <v>59</v>
@@ -9220,10 +9245,10 @@
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B410" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C410" t="s">
         <v>59</v>
@@ -9237,10 +9262,10 @@
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B411" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C411" t="s">
         <v>59</v>
@@ -9254,10 +9279,10 @@
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B412" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C412" t="s">
         <v>59</v>
@@ -9271,10 +9296,10 @@
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B413" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C413" t="s">
         <v>59</v>
@@ -9288,10 +9313,10 @@
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B414" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C414" t="s">
         <v>59</v>
@@ -9305,10 +9330,10 @@
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B415" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C415" t="s">
         <v>59</v>
@@ -9322,10 +9347,10 @@
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B416" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C416" t="s">
         <v>59</v>
@@ -9339,10 +9364,10 @@
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B417" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C417" t="s">
         <v>59</v>
@@ -9356,13 +9381,13 @@
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B418" t="s">
         <v>59</v>
       </c>
       <c r="C418" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D418">
         <v>1</v>
@@ -9373,13 +9398,13 @@
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B419" t="s">
         <v>59</v>
       </c>
       <c r="C419" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D419">
         <v>2</v>
@@ -9390,13 +9415,13 @@
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B420" t="s">
         <v>59</v>
       </c>
       <c r="C420" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D420">
         <v>3</v>
@@ -9407,13 +9432,13 @@
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B421" t="s">
         <v>59</v>
       </c>
       <c r="C421" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D421">
         <v>4</v>
@@ -9424,13 +9449,13 @@
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B422" t="s">
         <v>59</v>
       </c>
       <c r="C422" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D422">
         <v>5</v>
@@ -9441,13 +9466,13 @@
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B423" t="s">
         <v>59</v>
       </c>
       <c r="C423" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D423">
         <v>6</v>
@@ -9458,13 +9483,13 @@
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B424" t="s">
         <v>59</v>
       </c>
       <c r="C424" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D424">
         <v>7</v>
@@ -9475,13 +9500,13 @@
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B425" t="s">
         <v>59</v>
       </c>
       <c r="C425" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D425">
         <v>8</v>
@@ -9492,13 +9517,13 @@
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B426" t="s">
         <v>59</v>
       </c>
       <c r="C426" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D426">
         <v>9</v>
@@ -9509,13 +9534,13 @@
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B427" t="s">
         <v>59</v>
       </c>
       <c r="C427" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D427">
         <v>10</v>
@@ -9526,13 +9551,13 @@
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B428" t="s">
         <v>59</v>
       </c>
       <c r="C428" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D428">
         <v>11</v>
@@ -9543,13 +9568,13 @@
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B429" t="s">
         <v>59</v>
       </c>
       <c r="C429" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D429">
         <v>12</v>
@@ -9560,13 +9585,13 @@
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B430" t="s">
         <v>59</v>
       </c>
       <c r="C430" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D430">
         <v>13</v>
@@ -9577,13 +9602,13 @@
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B431" t="s">
         <v>59</v>
       </c>
       <c r="C431" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D431">
         <v>14</v>
@@ -9594,13 +9619,13 @@
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B432" t="s">
         <v>59</v>
       </c>
       <c r="C432" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D432">
         <v>15</v>
@@ -9611,13 +9636,13 @@
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B433" t="s">
         <v>59</v>
       </c>
       <c r="C433" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D433">
         <v>16</v>
@@ -9628,13 +9653,13 @@
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B434" t="s">
         <v>59</v>
       </c>
       <c r="C434" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D434">
         <v>17</v>
@@ -9645,13 +9670,13 @@
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B435" t="s">
         <v>59</v>
       </c>
       <c r="C435" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D435">
         <v>18</v>
@@ -9662,13 +9687,13 @@
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B436" t="s">
         <v>59</v>
       </c>
       <c r="C436" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D436">
         <v>19</v>
@@ -9679,13 +9704,13 @@
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B437" t="s">
         <v>59</v>
       </c>
       <c r="C437" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D437">
         <v>20</v>
@@ -9696,13 +9721,13 @@
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B438" t="s">
         <v>59</v>
       </c>
       <c r="C438" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D438">
         <v>21</v>
@@ -9713,13 +9738,13 @@
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B439" t="s">
         <v>59</v>
       </c>
       <c r="C439" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D439">
         <v>22</v>
@@ -9730,13 +9755,13 @@
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B440" t="s">
         <v>59</v>
       </c>
       <c r="C440" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D440">
         <v>23</v>
@@ -9747,13 +9772,13 @@
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B441" t="s">
         <v>59</v>
       </c>
       <c r="C441" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D441">
         <v>24</v>
@@ -9764,13 +9789,13 @@
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B442" t="s">
         <v>59</v>
       </c>
       <c r="C442" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D442">
         <v>25</v>
@@ -9781,13 +9806,13 @@
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B443" t="s">
         <v>59</v>
       </c>
       <c r="C443" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D443">
         <v>26</v>
@@ -9798,13 +9823,13 @@
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B444" t="s">
         <v>59</v>
       </c>
       <c r="C444" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D444">
         <v>1</v>
@@ -9815,13 +9840,13 @@
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B445" t="s">
         <v>59</v>
       </c>
       <c r="C445" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D445">
         <v>2</v>
@@ -9832,13 +9857,13 @@
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B446" t="s">
         <v>59</v>
       </c>
       <c r="C446" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D446">
         <v>3</v>
@@ -9849,13 +9874,13 @@
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B447" t="s">
         <v>59</v>
       </c>
       <c r="C447" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D447">
         <v>4</v>
@@ -9866,13 +9891,13 @@
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B448" t="s">
         <v>59</v>
       </c>
       <c r="C448" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D448">
         <v>5</v>
@@ -9883,13 +9908,13 @@
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B449" t="s">
         <v>59</v>
       </c>
       <c r="C449" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D449">
         <v>6</v>
@@ -9900,13 +9925,13 @@
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B450" t="s">
         <v>59</v>
       </c>
       <c r="C450" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D450">
         <v>7</v>
@@ -9917,13 +9942,13 @@
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B451" t="s">
         <v>59</v>
       </c>
       <c r="C451" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D451">
         <v>8</v>
@@ -9934,13 +9959,13 @@
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B452" t="s">
         <v>59</v>
       </c>
       <c r="C452" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D452">
         <v>9</v>
@@ -9951,13 +9976,13 @@
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B453" t="s">
         <v>59</v>
       </c>
       <c r="C453" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D453">
         <v>10</v>
@@ -9968,13 +9993,13 @@
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B454" t="s">
         <v>59</v>
       </c>
       <c r="C454" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D454">
         <v>11</v>
@@ -9985,13 +10010,13 @@
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B455" t="s">
         <v>59</v>
       </c>
       <c r="C455" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D455">
         <v>12</v>
@@ -10002,13 +10027,13 @@
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B456" t="s">
         <v>59</v>
       </c>
       <c r="C456" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D456">
         <v>13</v>
@@ -10019,13 +10044,13 @@
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B457" t="s">
         <v>59</v>
       </c>
       <c r="C457" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D457">
         <v>14</v>
@@ -10036,13 +10061,13 @@
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B458" t="s">
         <v>59</v>
       </c>
       <c r="C458" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D458">
         <v>15</v>
@@ -10053,13 +10078,13 @@
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B459" t="s">
         <v>59</v>
       </c>
       <c r="C459" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D459">
         <v>16</v>
@@ -10070,13 +10095,13 @@
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B460" t="s">
         <v>59</v>
       </c>
       <c r="C460" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D460">
         <v>17</v>
@@ -10087,13 +10112,13 @@
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B461" t="s">
         <v>59</v>
       </c>
       <c r="C461" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D461">
         <v>18</v>
@@ -10104,13 +10129,13 @@
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B462" t="s">
         <v>59</v>
       </c>
       <c r="C462" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D462">
         <v>19</v>
@@ -10121,13 +10146,13 @@
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B463" t="s">
         <v>59</v>
       </c>
       <c r="C463" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D463">
         <v>20</v>
@@ -10138,13 +10163,13 @@
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B464" t="s">
         <v>59</v>
       </c>
       <c r="C464" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D464">
         <v>21</v>
@@ -10155,13 +10180,13 @@
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B465" t="s">
         <v>59</v>
       </c>
       <c r="C465" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D465">
         <v>22</v>
@@ -10172,13 +10197,13 @@
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B466" t="s">
         <v>59</v>
       </c>
       <c r="C466" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D466">
         <v>23</v>
@@ -10189,13 +10214,13 @@
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B467" t="s">
         <v>59</v>
       </c>
       <c r="C467" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D467">
         <v>24</v>
@@ -10206,13 +10231,13 @@
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B468" t="s">
         <v>59</v>
       </c>
       <c r="C468" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D468">
         <v>25</v>
@@ -10223,13 +10248,13 @@
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B469" t="s">
         <v>59</v>
       </c>
       <c r="C469" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D469">
         <v>26</v>
@@ -10240,10 +10265,10 @@
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B470" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C470" t="s">
         <v>59</v>
@@ -10257,10 +10282,10 @@
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B471" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C471" t="s">
         <v>59</v>
@@ -10274,10 +10299,10 @@
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B472" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C472" t="s">
         <v>59</v>
@@ -10291,10 +10316,10 @@
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B473" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C473" t="s">
         <v>59</v>
@@ -10308,10 +10333,10 @@
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B474" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C474" t="s">
         <v>59</v>
@@ -10325,10 +10350,10 @@
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B475" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C475" t="s">
         <v>59</v>
@@ -10342,10 +10367,10 @@
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B476" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C476" t="s">
         <v>59</v>
@@ -10359,10 +10384,10 @@
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B477" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C477" t="s">
         <v>59</v>
@@ -10376,10 +10401,10 @@
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B478" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C478" t="s">
         <v>59</v>
@@ -10393,10 +10418,10 @@
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B479" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C479" t="s">
         <v>59</v>
@@ -10410,10 +10435,10 @@
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B480" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C480" t="s">
         <v>59</v>
@@ -10427,10 +10452,10 @@
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B481" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C481" t="s">
         <v>59</v>
@@ -10444,10 +10469,10 @@
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B482" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C482" t="s">
         <v>59</v>
@@ -10461,10 +10486,10 @@
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B483" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C483" t="s">
         <v>59</v>
@@ -10478,10 +10503,10 @@
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B484" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C484" t="s">
         <v>59</v>
@@ -10495,10 +10520,10 @@
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B485" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C485" t="s">
         <v>59</v>
@@ -10512,10 +10537,10 @@
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B486" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C486" t="s">
         <v>59</v>
@@ -10529,10 +10554,10 @@
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B487" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C487" t="s">
         <v>59</v>
@@ -10546,10 +10571,10 @@
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B488" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C488" t="s">
         <v>59</v>
@@ -10563,10 +10588,10 @@
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B489" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C489" t="s">
         <v>59</v>
@@ -10580,10 +10605,10 @@
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B490" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C490" t="s">
         <v>59</v>
@@ -10597,10 +10622,10 @@
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B491" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C491" t="s">
         <v>59</v>
@@ -10614,10 +10639,10 @@
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B492" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C492" t="s">
         <v>59</v>
@@ -10631,10 +10656,10 @@
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B493" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C493" t="s">
         <v>59</v>
@@ -10648,10 +10673,10 @@
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B494" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C494" t="s">
         <v>59</v>
@@ -10665,10 +10690,10 @@
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B495" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C495" t="s">
         <v>59</v>
@@ -10682,13 +10707,13 @@
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B496" t="s">
         <v>59</v>
       </c>
       <c r="C496" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D496">
         <v>1</v>
@@ -10699,13 +10724,13 @@
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B497" t="s">
         <v>59</v>
       </c>
       <c r="C497" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D497">
         <v>2</v>
@@ -10716,13 +10741,13 @@
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B498" t="s">
         <v>59</v>
       </c>
       <c r="C498" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D498">
         <v>3</v>
@@ -10733,13 +10758,13 @@
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B499" t="s">
         <v>59</v>
       </c>
       <c r="C499" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D499">
         <v>4</v>
@@ -10750,13 +10775,13 @@
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B500" t="s">
         <v>59</v>
       </c>
       <c r="C500" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D500">
         <v>5</v>
@@ -10767,13 +10792,13 @@
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B501" t="s">
         <v>59</v>
       </c>
       <c r="C501" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D501">
         <v>6</v>
@@ -10784,13 +10809,13 @@
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B502" t="s">
         <v>59</v>
       </c>
       <c r="C502" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D502">
         <v>7</v>
@@ -10801,13 +10826,13 @@
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B503" t="s">
         <v>59</v>
       </c>
       <c r="C503" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D503">
         <v>8</v>
@@ -10818,13 +10843,13 @@
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B504" t="s">
         <v>59</v>
       </c>
       <c r="C504" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D504">
         <v>9</v>
@@ -10835,13 +10860,13 @@
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B505" t="s">
         <v>59</v>
       </c>
       <c r="C505" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D505">
         <v>10</v>
@@ -10852,13 +10877,13 @@
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B506" t="s">
         <v>59</v>
       </c>
       <c r="C506" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D506">
         <v>11</v>
@@ -10869,13 +10894,13 @@
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B507" t="s">
         <v>59</v>
       </c>
       <c r="C507" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D507">
         <v>12</v>
@@ -10886,13 +10911,13 @@
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B508" t="s">
         <v>59</v>
       </c>
       <c r="C508" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D508">
         <v>13</v>
@@ -10903,13 +10928,13 @@
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B509" t="s">
         <v>59</v>
       </c>
       <c r="C509" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D509">
         <v>14</v>
@@ -10920,13 +10945,13 @@
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B510" t="s">
         <v>59</v>
       </c>
       <c r="C510" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D510">
         <v>15</v>
@@ -10937,13 +10962,13 @@
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B511" t="s">
         <v>59</v>
       </c>
       <c r="C511" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D511">
         <v>16</v>
@@ -10954,13 +10979,13 @@
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B512" t="s">
         <v>59</v>
       </c>
       <c r="C512" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D512">
         <v>17</v>
@@ -10971,13 +10996,13 @@
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B513" t="s">
         <v>59</v>
       </c>
       <c r="C513" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D513">
         <v>18</v>
@@ -10988,13 +11013,13 @@
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B514" t="s">
         <v>59</v>
       </c>
       <c r="C514" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D514">
         <v>19</v>
@@ -11005,13 +11030,13 @@
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B515" t="s">
         <v>59</v>
       </c>
       <c r="C515" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D515">
         <v>20</v>
@@ -11022,13 +11047,13 @@
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B516" t="s">
         <v>59</v>
       </c>
       <c r="C516" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D516">
         <v>21</v>
@@ -11039,13 +11064,13 @@
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B517" t="s">
         <v>59</v>
       </c>
       <c r="C517" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D517">
         <v>22</v>
@@ -11056,13 +11081,13 @@
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B518" t="s">
         <v>59</v>
       </c>
       <c r="C518" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D518">
         <v>23</v>
@@ -11073,13 +11098,13 @@
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B519" t="s">
         <v>59</v>
       </c>
       <c r="C519" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D519">
         <v>24</v>
@@ -11090,13 +11115,13 @@
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B520" t="s">
         <v>59</v>
       </c>
       <c r="C520" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D520">
         <v>25</v>
@@ -11107,13 +11132,13 @@
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B521" t="s">
         <v>59</v>
       </c>
       <c r="C521" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D521">
         <v>26</v>
@@ -11124,10 +11149,10 @@
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B522" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C522" t="s">
         <v>59</v>
@@ -11141,10 +11166,10 @@
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B523" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C523" t="s">
         <v>59</v>
@@ -11158,10 +11183,10 @@
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B524" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C524" t="s">
         <v>59</v>
@@ -11175,10 +11200,10 @@
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B525" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C525" t="s">
         <v>59</v>
@@ -11192,10 +11217,10 @@
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B526" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C526" t="s">
         <v>59</v>
@@ -11209,10 +11234,10 @@
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B527" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C527" t="s">
         <v>59</v>
@@ -11226,10 +11251,10 @@
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B528" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C528" t="s">
         <v>59</v>
@@ -11243,10 +11268,10 @@
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B529" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C529" t="s">
         <v>59</v>
@@ -11260,10 +11285,10 @@
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B530" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C530" t="s">
         <v>59</v>
@@ -11277,10 +11302,10 @@
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B531" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C531" t="s">
         <v>59</v>
@@ -11294,10 +11319,10 @@
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B532" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C532" t="s">
         <v>59</v>
@@ -11311,10 +11336,10 @@
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B533" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C533" t="s">
         <v>59</v>
@@ -11328,10 +11353,10 @@
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B534" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C534" t="s">
         <v>59</v>
@@ -11345,10 +11370,10 @@
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B535" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C535" t="s">
         <v>59</v>
@@ -11362,10 +11387,10 @@
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B536" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C536" t="s">
         <v>59</v>
@@ -11379,10 +11404,10 @@
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B537" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C537" t="s">
         <v>59</v>
@@ -11396,10 +11421,10 @@
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B538" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C538" t="s">
         <v>59</v>
@@ -11413,10 +11438,10 @@
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B539" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C539" t="s">
         <v>59</v>
@@ -11430,10 +11455,10 @@
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B540" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C540" t="s">
         <v>59</v>
@@ -11447,10 +11472,10 @@
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B541" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C541" t="s">
         <v>59</v>
@@ -11464,10 +11489,10 @@
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B542" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C542" t="s">
         <v>59</v>
@@ -11481,10 +11506,10 @@
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B543" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C543" t="s">
         <v>59</v>
@@ -11498,10 +11523,10 @@
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B544" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C544" t="s">
         <v>59</v>
@@ -11515,10 +11540,10 @@
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B545" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C545" t="s">
         <v>59</v>
@@ -11532,10 +11557,10 @@
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B546" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C546" t="s">
         <v>59</v>
@@ -11549,10 +11574,10 @@
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B547" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C547" t="s">
         <v>59</v>
@@ -11566,13 +11591,13 @@
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B548" t="s">
         <v>59</v>
       </c>
       <c r="C548" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D548">
         <v>1</v>
@@ -11583,13 +11608,13 @@
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B549" t="s">
         <v>59</v>
       </c>
       <c r="C549" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D549">
         <v>2</v>
@@ -11600,13 +11625,13 @@
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B550" t="s">
         <v>59</v>
       </c>
       <c r="C550" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D550">
         <v>3</v>
@@ -11617,13 +11642,13 @@
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B551" t="s">
         <v>59</v>
       </c>
       <c r="C551" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D551">
         <v>4</v>
@@ -11634,13 +11659,13 @@
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B552" t="s">
         <v>59</v>
       </c>
       <c r="C552" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D552">
         <v>5</v>
@@ -11651,13 +11676,13 @@
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B553" t="s">
         <v>59</v>
       </c>
       <c r="C553" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D553">
         <v>6</v>
@@ -11668,13 +11693,13 @@
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B554" t="s">
         <v>59</v>
       </c>
       <c r="C554" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D554">
         <v>7</v>
@@ -11685,13 +11710,13 @@
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B555" t="s">
         <v>59</v>
       </c>
       <c r="C555" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D555">
         <v>8</v>
@@ -11702,13 +11727,13 @@
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B556" t="s">
         <v>59</v>
       </c>
       <c r="C556" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D556">
         <v>9</v>
@@ -11719,13 +11744,13 @@
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B557" t="s">
         <v>59</v>
       </c>
       <c r="C557" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D557">
         <v>10</v>
@@ -11736,13 +11761,13 @@
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B558" t="s">
         <v>59</v>
       </c>
       <c r="C558" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D558">
         <v>11</v>
@@ -11753,13 +11778,13 @@
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B559" t="s">
         <v>59</v>
       </c>
       <c r="C559" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D559">
         <v>12</v>
@@ -11770,13 +11795,13 @@
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B560" t="s">
         <v>59</v>
       </c>
       <c r="C560" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D560">
         <v>13</v>
@@ -11787,13 +11812,13 @@
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B561" t="s">
         <v>59</v>
       </c>
       <c r="C561" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D561">
         <v>14</v>
@@ -11804,13 +11829,13 @@
     </row>
     <row r="562" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B562" t="s">
         <v>59</v>
       </c>
       <c r="C562" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D562">
         <v>15</v>
@@ -11821,13 +11846,13 @@
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B563" t="s">
         <v>59</v>
       </c>
       <c r="C563" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D563">
         <v>16</v>
@@ -11838,13 +11863,13 @@
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B564" t="s">
         <v>59</v>
       </c>
       <c r="C564" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D564">
         <v>17</v>
@@ -11855,13 +11880,13 @@
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B565" t="s">
         <v>59</v>
       </c>
       <c r="C565" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D565">
         <v>18</v>
@@ -11872,13 +11897,13 @@
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B566" t="s">
         <v>59</v>
       </c>
       <c r="C566" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D566">
         <v>19</v>
@@ -11889,13 +11914,13 @@
     </row>
     <row r="567" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B567" t="s">
         <v>59</v>
       </c>
       <c r="C567" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D567">
         <v>20</v>
@@ -11906,13 +11931,13 @@
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B568" t="s">
         <v>59</v>
       </c>
       <c r="C568" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D568">
         <v>21</v>
@@ -11923,13 +11948,13 @@
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B569" t="s">
         <v>59</v>
       </c>
       <c r="C569" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D569">
         <v>22</v>
@@ -11940,13 +11965,13 @@
     </row>
     <row r="570" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B570" t="s">
         <v>59</v>
       </c>
       <c r="C570" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D570">
         <v>23</v>
@@ -11957,13 +11982,13 @@
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B571" t="s">
         <v>59</v>
       </c>
       <c r="C571" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D571">
         <v>24</v>
@@ -11974,13 +11999,13 @@
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B572" t="s">
         <v>59</v>
       </c>
       <c r="C572" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D572">
         <v>25</v>
@@ -11991,13 +12016,13 @@
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B573" t="s">
         <v>59</v>
       </c>
       <c r="C573" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D573">
         <v>26</v>
@@ -12008,10 +12033,10 @@
     </row>
     <row r="574" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B574" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C574" t="s">
         <v>59</v>
@@ -12025,10 +12050,10 @@
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B575" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C575" t="s">
         <v>59</v>
@@ -12042,10 +12067,10 @@
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B576" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C576" t="s">
         <v>59</v>
@@ -12059,10 +12084,10 @@
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B577" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C577" t="s">
         <v>59</v>
@@ -12076,10 +12101,10 @@
     </row>
     <row r="578" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B578" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C578" t="s">
         <v>59</v>
@@ -12093,10 +12118,10 @@
     </row>
     <row r="579" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B579" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C579" t="s">
         <v>59</v>
@@ -12110,10 +12135,10 @@
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B580" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C580" t="s">
         <v>59</v>
@@ -12127,10 +12152,10 @@
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B581" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C581" t="s">
         <v>59</v>
@@ -12144,10 +12169,10 @@
     </row>
     <row r="582" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B582" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C582" t="s">
         <v>59</v>
@@ -12161,10 +12186,10 @@
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B583" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C583" t="s">
         <v>59</v>
@@ -12178,10 +12203,10 @@
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B584" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C584" t="s">
         <v>59</v>
@@ -12195,10 +12220,10 @@
     </row>
     <row r="585" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B585" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C585" t="s">
         <v>59</v>
@@ -12212,10 +12237,10 @@
     </row>
     <row r="586" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B586" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C586" t="s">
         <v>59</v>
@@ -12229,10 +12254,10 @@
     </row>
     <row r="587" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B587" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C587" t="s">
         <v>59</v>
@@ -12246,10 +12271,10 @@
     </row>
     <row r="588" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B588" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C588" t="s">
         <v>59</v>
@@ -12263,10 +12288,10 @@
     </row>
     <row r="589" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A589" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B589" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C589" t="s">
         <v>59</v>
@@ -12280,10 +12305,10 @@
     </row>
     <row r="590" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A590" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B590" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C590" t="s">
         <v>59</v>
@@ -12297,10 +12322,10 @@
     </row>
     <row r="591" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A591" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B591" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C591" t="s">
         <v>59</v>
@@ -12314,10 +12339,10 @@
     </row>
     <row r="592" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A592" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B592" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C592" t="s">
         <v>59</v>
@@ -12331,10 +12356,10 @@
     </row>
     <row r="593" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A593" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B593" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C593" t="s">
         <v>59</v>
@@ -12348,10 +12373,10 @@
     </row>
     <row r="594" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B594" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C594" t="s">
         <v>59</v>
@@ -12365,10 +12390,10 @@
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A595" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B595" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C595" t="s">
         <v>59</v>
@@ -12382,10 +12407,10 @@
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A596" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B596" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C596" t="s">
         <v>59</v>
@@ -12399,10 +12424,10 @@
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A597" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B597" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C597" t="s">
         <v>59</v>
@@ -12416,10 +12441,10 @@
     </row>
     <row r="598" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A598" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B598" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C598" t="s">
         <v>59</v>
@@ -12433,10 +12458,10 @@
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A599" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B599" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C599" t="s">
         <v>59</v>
@@ -12450,13 +12475,13 @@
     </row>
     <row r="600" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A600" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B600" t="s">
         <v>59</v>
       </c>
       <c r="C600" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D600">
         <v>1</v>
@@ -12467,13 +12492,13 @@
     </row>
     <row r="601" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A601" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B601" t="s">
         <v>59</v>
       </c>
       <c r="C601" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D601">
         <v>2</v>
@@ -12484,13 +12509,13 @@
     </row>
     <row r="602" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A602" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B602" t="s">
         <v>59</v>
       </c>
       <c r="C602" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D602">
         <v>3</v>
@@ -12501,13 +12526,13 @@
     </row>
     <row r="603" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A603" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B603" t="s">
         <v>59</v>
       </c>
       <c r="C603" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D603">
         <v>4</v>
@@ -12518,13 +12543,13 @@
     </row>
     <row r="604" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A604" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B604" t="s">
         <v>59</v>
       </c>
       <c r="C604" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D604">
         <v>5</v>
@@ -12535,13 +12560,13 @@
     </row>
     <row r="605" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A605" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B605" t="s">
         <v>59</v>
       </c>
       <c r="C605" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D605">
         <v>6</v>
@@ -12552,13 +12577,13 @@
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A606" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B606" t="s">
         <v>59</v>
       </c>
       <c r="C606" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D606">
         <v>7</v>
@@ -12569,13 +12594,13 @@
     </row>
     <row r="607" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A607" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B607" t="s">
         <v>59</v>
       </c>
       <c r="C607" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D607">
         <v>8</v>
@@ -12586,13 +12611,13 @@
     </row>
     <row r="608" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A608" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B608" t="s">
         <v>59</v>
       </c>
       <c r="C608" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D608">
         <v>9</v>
@@ -12603,13 +12628,13 @@
     </row>
     <row r="609" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A609" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B609" t="s">
         <v>59</v>
       </c>
       <c r="C609" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D609">
         <v>10</v>
@@ -12620,13 +12645,13 @@
     </row>
     <row r="610" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A610" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B610" t="s">
         <v>59</v>
       </c>
       <c r="C610" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D610">
         <v>11</v>
@@ -12637,13 +12662,13 @@
     </row>
     <row r="611" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A611" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B611" t="s">
         <v>59</v>
       </c>
       <c r="C611" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D611">
         <v>12</v>
@@ -12654,13 +12679,13 @@
     </row>
     <row r="612" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A612" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B612" t="s">
         <v>59</v>
       </c>
       <c r="C612" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D612">
         <v>13</v>
@@ -12671,13 +12696,13 @@
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A613" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B613" t="s">
         <v>59</v>
       </c>
       <c r="C613" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D613">
         <v>14</v>
@@ -12688,13 +12713,13 @@
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A614" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B614" t="s">
         <v>59</v>
       </c>
       <c r="C614" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D614">
         <v>15</v>
@@ -12705,13 +12730,13 @@
     </row>
     <row r="615" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A615" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B615" t="s">
         <v>59</v>
       </c>
       <c r="C615" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D615">
         <v>16</v>
@@ -12722,13 +12747,13 @@
     </row>
     <row r="616" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A616" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B616" t="s">
         <v>59</v>
       </c>
       <c r="C616" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D616">
         <v>17</v>
@@ -12739,13 +12764,13 @@
     </row>
     <row r="617" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A617" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B617" t="s">
         <v>59</v>
       </c>
       <c r="C617" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D617">
         <v>18</v>
@@ -12756,13 +12781,13 @@
     </row>
     <row r="618" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A618" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B618" t="s">
         <v>59</v>
       </c>
       <c r="C618" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D618">
         <v>19</v>
@@ -12773,13 +12798,13 @@
     </row>
     <row r="619" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A619" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B619" t="s">
         <v>59</v>
       </c>
       <c r="C619" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D619">
         <v>20</v>
@@ -12790,13 +12815,13 @@
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A620" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B620" t="s">
         <v>59</v>
       </c>
       <c r="C620" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D620">
         <v>21</v>
@@ -12807,13 +12832,13 @@
     </row>
     <row r="621" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A621" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B621" t="s">
         <v>59</v>
       </c>
       <c r="C621" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D621">
         <v>22</v>
@@ -12824,13 +12849,13 @@
     </row>
     <row r="622" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A622" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B622" t="s">
         <v>59</v>
       </c>
       <c r="C622" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D622">
         <v>23</v>
@@ -12841,13 +12866,13 @@
     </row>
     <row r="623" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A623" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B623" t="s">
         <v>59</v>
       </c>
       <c r="C623" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D623">
         <v>24</v>
@@ -12858,13 +12883,13 @@
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A624" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B624" t="s">
         <v>59</v>
       </c>
       <c r="C624" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D624">
         <v>25</v>
@@ -12875,13 +12900,13 @@
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A625" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B625" t="s">
         <v>59</v>
       </c>
       <c r="C625" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D625">
         <v>26</v>
@@ -12892,7 +12917,7 @@
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A626" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B626" t="s">
         <v>58</v>
@@ -12909,7 +12934,7 @@
     </row>
     <row r="627" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A627" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B627" t="s">
         <v>58</v>
@@ -12926,7 +12951,7 @@
     </row>
     <row r="628" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A628" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B628" t="s">
         <v>58</v>
@@ -12943,7 +12968,7 @@
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A629" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B629" t="s">
         <v>58</v>
@@ -12960,7 +12985,7 @@
     </row>
     <row r="630" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A630" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B630" t="s">
         <v>58</v>
@@ -12977,7 +13002,7 @@
     </row>
     <row r="631" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A631" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B631" t="s">
         <v>58</v>
@@ -12994,7 +13019,7 @@
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A632" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B632" t="s">
         <v>58</v>
@@ -13011,7 +13036,7 @@
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A633" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B633" t="s">
         <v>58</v>
@@ -13028,7 +13053,7 @@
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A634" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B634" t="s">
         <v>58</v>
@@ -13045,7 +13070,7 @@
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A635" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B635" t="s">
         <v>58</v>
@@ -13062,7 +13087,7 @@
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A636" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B636" t="s">
         <v>58</v>
@@ -13079,7 +13104,7 @@
     </row>
     <row r="637" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A637" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B637" t="s">
         <v>58</v>
@@ -13096,7 +13121,7 @@
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A638" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B638" t="s">
         <v>58</v>
@@ -13113,7 +13138,7 @@
     </row>
     <row r="639" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A639" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B639" t="s">
         <v>58</v>
@@ -13130,7 +13155,7 @@
     </row>
     <row r="640" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A640" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B640" t="s">
         <v>58</v>
@@ -13147,7 +13172,7 @@
     </row>
     <row r="641" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A641" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B641" t="s">
         <v>58</v>
@@ -13164,7 +13189,7 @@
     </row>
     <row r="642" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A642" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B642" t="s">
         <v>58</v>
@@ -13181,7 +13206,7 @@
     </row>
     <row r="643" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A643" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B643" t="s">
         <v>58</v>
@@ -13198,7 +13223,7 @@
     </row>
     <row r="644" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A644" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B644" t="s">
         <v>58</v>
@@ -13215,7 +13240,7 @@
     </row>
     <row r="645" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A645" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B645" t="s">
         <v>58</v>
@@ -13232,7 +13257,7 @@
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A646" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B646" t="s">
         <v>58</v>
@@ -13249,7 +13274,7 @@
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A647" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B647" t="s">
         <v>58</v>
@@ -13266,7 +13291,7 @@
     </row>
     <row r="648" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A648" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B648" t="s">
         <v>58</v>
@@ -13283,7 +13308,7 @@
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A649" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B649" t="s">
         <v>58</v>
@@ -13300,7 +13325,7 @@
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A650" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B650" t="s">
         <v>58</v>
@@ -13317,7 +13342,7 @@
     </row>
     <row r="651" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A651" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B651" t="s">
         <v>58</v>
@@ -13352,172 +13377,172 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1" t="s">
         <v>138</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>139</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>140</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>141</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>142</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>143</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>144</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>145</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>146</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>147</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>148</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>149</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>150</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>151</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>152</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>153</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>154</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>155</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>156</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>157</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>158</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>159</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>160</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>161</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>162</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>163</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>164</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>165</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>166</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>167</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>168</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>169</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>170</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>171</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>172</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>173</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>174</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>175</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>176</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>177</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>178</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>179</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>180</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>181</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>182</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>183</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>184</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>185</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>186</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>187</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>188</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>189</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>190</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>191</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>192</v>
-      </c>
-      <c r="BE1" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:57" x14ac:dyDescent="0.2">

--- a/SVTwello/zondag2.xlsx
+++ b/SVTwello/zondag2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rodi/Documents/Zondag2/SVTwello/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2F3DDB-6020-414D-B147-265CF5588368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F194E1C-ED13-D34F-B295-79275A4B6001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="34560" windowHeight="20580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="34560" windowHeight="20580" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="spelers" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2984" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3033" uniqueCount="203">
   <si>
     <t>speler_id</t>
   </si>
@@ -646,6 +646,9 @@
   </si>
   <si>
     <t>2-3</t>
+  </si>
+  <si>
+    <t>3-0</t>
   </si>
 </sst>
 </file>
@@ -1716,7 +1719,9 @@
       <c r="E3" t="s">
         <v>64</v>
       </c>
-      <c r="F3" s="1"/>
+      <c r="F3" s="1" t="s">
+        <v>202</v>
+      </c>
       <c r="G3" t="s">
         <v>60</v>
       </c>
@@ -2361,6 +2366,9 @@
       <c r="E6" t="s">
         <v>15</v>
       </c>
+      <c r="G6" t="s">
+        <v>133</v>
+      </c>
       <c r="H6">
         <v>1</v>
       </c>
@@ -2387,6 +2395,9 @@
       <c r="E7" t="s">
         <v>17</v>
       </c>
+      <c r="G7" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -2404,6 +2415,9 @@
       <c r="E8" t="s">
         <v>18</v>
       </c>
+      <c r="G8" t="s">
+        <v>133</v>
+      </c>
       <c r="H8">
         <v>1</v>
       </c>
@@ -2424,6 +2438,9 @@
       <c r="E9" t="s">
         <v>19</v>
       </c>
+      <c r="G9" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -2441,6 +2458,9 @@
       <c r="E10" t="s">
         <v>21</v>
       </c>
+      <c r="G10" t="s">
+        <v>133</v>
+      </c>
       <c r="H10">
         <v>1</v>
       </c>
@@ -2461,6 +2481,9 @@
       <c r="E11" t="s">
         <v>23</v>
       </c>
+      <c r="G11" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -2478,6 +2501,9 @@
       <c r="E12" t="s">
         <v>24</v>
       </c>
+      <c r="G12" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -2495,6 +2521,12 @@
       <c r="E13" t="s">
         <v>25</v>
       </c>
+      <c r="G13" t="s">
+        <v>133</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -2512,6 +2544,9 @@
       <c r="E14" t="s">
         <v>26</v>
       </c>
+      <c r="G14" t="s">
+        <v>133</v>
+      </c>
       <c r="J14">
         <v>1</v>
       </c>
@@ -2532,6 +2567,9 @@
       <c r="E15" t="s">
         <v>27</v>
       </c>
+      <c r="G15" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -2549,6 +2587,12 @@
       <c r="E16" t="s">
         <v>28</v>
       </c>
+      <c r="G16" t="s">
+        <v>133</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
       <c r="J16">
         <v>1</v>
       </c>
@@ -2569,6 +2613,9 @@
       <c r="E17" t="s">
         <v>29</v>
       </c>
+      <c r="G17" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
@@ -2589,6 +2636,9 @@
       <c r="F18">
         <v>1</v>
       </c>
+      <c r="G18" t="s">
+        <v>135</v>
+      </c>
       <c r="K18">
         <v>1</v>
       </c>
@@ -2609,6 +2659,9 @@
       <c r="E19" t="s">
         <v>31</v>
       </c>
+      <c r="G19" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
@@ -2626,6 +2679,12 @@
       <c r="E20" t="s">
         <v>33</v>
       </c>
+      <c r="G20" t="s">
+        <v>133</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
@@ -2643,6 +2702,9 @@
       <c r="E21" t="s">
         <v>34</v>
       </c>
+      <c r="G21" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
@@ -2660,6 +2722,9 @@
       <c r="E22" t="s">
         <v>35</v>
       </c>
+      <c r="G22" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
@@ -2677,6 +2742,9 @@
       <c r="E23" t="s">
         <v>37</v>
       </c>
+      <c r="G23" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
@@ -2694,6 +2762,9 @@
       <c r="E24" t="s">
         <v>38</v>
       </c>
+      <c r="G24" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
@@ -2714,6 +2785,9 @@
       <c r="F25">
         <v>1</v>
       </c>
+      <c r="G25" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
@@ -2731,6 +2805,9 @@
       <c r="E26" t="s">
         <v>40</v>
       </c>
+      <c r="G26" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
@@ -2748,6 +2825,9 @@
       <c r="E27" t="s">
         <v>41</v>
       </c>
+      <c r="G27" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
@@ -2765,6 +2845,9 @@
       <c r="E28" t="s">
         <v>7</v>
       </c>
+      <c r="G28" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
@@ -2782,6 +2865,9 @@
       <c r="E29" t="s">
         <v>11</v>
       </c>
+      <c r="G29" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
@@ -2799,6 +2885,9 @@
       <c r="E30" t="s">
         <v>13</v>
       </c>
+      <c r="G30" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
@@ -2816,6 +2905,9 @@
       <c r="E31" t="s">
         <v>14</v>
       </c>
+      <c r="G31" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
@@ -2833,8 +2925,11 @@
       <c r="E32" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G32" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>61</v>
       </c>
@@ -2850,8 +2945,11 @@
       <c r="E33" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G33" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>61</v>
       </c>
@@ -2867,8 +2965,14 @@
       <c r="E34" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G34" t="s">
+        <v>135</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>61</v>
       </c>
@@ -2884,8 +2988,14 @@
       <c r="E35" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G35" t="s">
+        <v>135</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>61</v>
       </c>
@@ -2901,8 +3011,11 @@
       <c r="E36" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G36" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>61</v>
       </c>
@@ -2918,8 +3031,11 @@
       <c r="E37" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G37" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>61</v>
       </c>
@@ -2935,8 +3051,11 @@
       <c r="E38" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G38" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>61</v>
       </c>
@@ -2952,8 +3071,11 @@
       <c r="E39" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G39" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>61</v>
       </c>
@@ -2969,8 +3091,11 @@
       <c r="E40" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G40" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>61</v>
       </c>
@@ -2986,8 +3111,11 @@
       <c r="E41" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G41" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>61</v>
       </c>
@@ -3003,8 +3131,14 @@
       <c r="E42" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G42" t="s">
+        <v>135</v>
+      </c>
+      <c r="K42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>61</v>
       </c>
@@ -3020,8 +3154,11 @@
       <c r="E43" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G43" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>61</v>
       </c>
@@ -3037,8 +3174,14 @@
       <c r="E44" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G44" t="s">
+        <v>135</v>
+      </c>
+      <c r="H44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>61</v>
       </c>
@@ -3054,8 +3197,11 @@
       <c r="E45" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G45" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>61</v>
       </c>
@@ -3071,8 +3217,11 @@
       <c r="E46" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G46" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>61</v>
       </c>
@@ -3088,8 +3237,14 @@
       <c r="E47" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G47" t="s">
+        <v>135</v>
+      </c>
+      <c r="H47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>61</v>
       </c>
@@ -3105,8 +3260,14 @@
       <c r="E48" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G48" t="s">
+        <v>135</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>61</v>
       </c>
@@ -3122,8 +3283,14 @@
       <c r="E49" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G49" t="s">
+        <v>135</v>
+      </c>
+      <c r="I49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>61</v>
       </c>
@@ -3139,8 +3306,11 @@
       <c r="E50" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G50" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>61</v>
       </c>
@@ -3156,8 +3326,11 @@
       <c r="E51" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G51" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>61</v>
       </c>
@@ -3173,8 +3346,11 @@
       <c r="E52" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G52" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>61</v>
       </c>
@@ -3190,8 +3366,11 @@
       <c r="E53" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G53" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>65</v>
       </c>
@@ -3208,7 +3387,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>65</v>
       </c>
@@ -3225,7 +3404,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>65</v>
       </c>
@@ -3242,7 +3421,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>65</v>
       </c>
@@ -3259,7 +3438,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -3276,7 +3455,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>65</v>
       </c>
@@ -3293,7 +3472,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>65</v>
       </c>
@@ -3310,7 +3489,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>65</v>
       </c>
@@ -3327,7 +3506,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>65</v>
       </c>
@@ -3344,7 +3523,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>65</v>
       </c>
@@ -3361,7 +3540,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>65</v>
       </c>

--- a/SVTwello/zondag2.xlsx
+++ b/SVTwello/zondag2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rodi/Documents/Zondag2/SVTwello/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F194E1C-ED13-D34F-B295-79275A4B6001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99AE3106-FB0A-A44D-A313-C1F30BECC11B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="34560" windowHeight="20580" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20580" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="spelers" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3033" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3034" uniqueCount="204">
   <si>
     <t>speler_id</t>
   </si>
@@ -649,6 +649,9 @@
   </si>
   <si>
     <t>3-0</t>
+  </si>
+  <si>
+    <t>aanwezig</t>
   </si>
 </sst>
 </file>
@@ -2216,23 +2219,23 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:L651"/>
+  <dimension ref="A1:M651"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.5" customWidth="1"/>
-    <col min="7" max="7" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="16.5" customWidth="1"/>
+    <col min="8" max="8" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>48</v>
       </c>
@@ -2252,25 +2255,28 @@
         <v>194</v>
       </c>
       <c r="G1" t="s">
+        <v>203</v>
+      </c>
+      <c r="H1" t="s">
         <v>127</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>128</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>129</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>130</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>131</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>55</v>
       </c>
@@ -2286,11 +2292,14 @@
       <c r="E2" t="s">
         <v>7</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>55</v>
       </c>
@@ -2306,11 +2315,14 @@
       <c r="E3" t="s">
         <v>11</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>55</v>
       </c>
@@ -2326,11 +2338,14 @@
       <c r="E4" t="s">
         <v>13</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>55</v>
       </c>
@@ -2346,11 +2361,14 @@
       <c r="E5" t="s">
         <v>14</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>55</v>
       </c>
@@ -2366,20 +2384,23 @@
       <c r="E6" t="s">
         <v>15</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6" t="s">
         <v>133</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>1</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>1</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>55</v>
       </c>
@@ -2395,11 +2416,14 @@
       <c r="E7" t="s">
         <v>17</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>55</v>
       </c>
@@ -2415,14 +2439,17 @@
       <c r="E8" t="s">
         <v>18</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
         <v>133</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>55</v>
       </c>
@@ -2438,11 +2465,14 @@
       <c r="E9" t="s">
         <v>19</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>55</v>
       </c>
@@ -2458,14 +2488,17 @@
       <c r="E10" t="s">
         <v>21</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
         <v>133</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -2481,11 +2514,14 @@
       <c r="E11" t="s">
         <v>23</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>55</v>
       </c>
@@ -2501,11 +2537,14 @@
       <c r="E12" t="s">
         <v>24</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -2521,14 +2560,17 @@
       <c r="E13" t="s">
         <v>25</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13" t="s">
         <v>133</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>55</v>
       </c>
@@ -2544,14 +2586,17 @@
       <c r="E14" t="s">
         <v>26</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
         <v>133</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>55</v>
       </c>
@@ -2567,11 +2612,14 @@
       <c r="E15" t="s">
         <v>27</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>55</v>
       </c>
@@ -2587,17 +2635,20 @@
       <c r="E16" t="s">
         <v>28</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16" t="s">
         <v>133</v>
-      </c>
-      <c r="I16">
-        <v>1</v>
       </c>
       <c r="J16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -2613,11 +2664,14 @@
       <c r="E17" t="s">
         <v>29</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>55</v>
       </c>
@@ -2636,14 +2690,17 @@
       <c r="F18">
         <v>1</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18" t="s">
         <v>135</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>55</v>
       </c>
@@ -2659,11 +2716,14 @@
       <c r="E19" t="s">
         <v>31</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>55</v>
       </c>
@@ -2679,14 +2739,17 @@
       <c r="E20" t="s">
         <v>33</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20" t="s">
         <v>133</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>55</v>
       </c>
@@ -2702,11 +2765,14 @@
       <c r="E21" t="s">
         <v>34</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -2722,11 +2788,14 @@
       <c r="E22" t="s">
         <v>35</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -2742,11 +2811,14 @@
       <c r="E23" t="s">
         <v>37</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -2762,11 +2834,14 @@
       <c r="E24" t="s">
         <v>38</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -2785,11 +2860,14 @@
       <c r="F25">
         <v>1</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -2805,11 +2883,14 @@
       <c r="E26" t="s">
         <v>40</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -2825,11 +2906,14 @@
       <c r="E27" t="s">
         <v>41</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>61</v>
       </c>
@@ -2845,11 +2929,11 @@
       <c r="E28" t="s">
         <v>7</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>61</v>
       </c>
@@ -2865,11 +2949,11 @@
       <c r="E29" t="s">
         <v>11</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -2885,11 +2969,11 @@
       <c r="E30" t="s">
         <v>13</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>61</v>
       </c>
@@ -2905,11 +2989,11 @@
       <c r="E31" t="s">
         <v>14</v>
       </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>61</v>
       </c>
@@ -2925,11 +3009,11 @@
       <c r="E32" t="s">
         <v>15</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>61</v>
       </c>
@@ -2945,11 +3029,11 @@
       <c r="E33" t="s">
         <v>17</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>61</v>
       </c>
@@ -2965,14 +3049,14 @@
       <c r="E34" t="s">
         <v>18</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>135</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>61</v>
       </c>
@@ -2988,14 +3072,14 @@
       <c r="E35" t="s">
         <v>19</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
         <v>135</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>61</v>
       </c>
@@ -3011,11 +3095,11 @@
       <c r="E36" t="s">
         <v>21</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>61</v>
       </c>
@@ -3031,11 +3115,11 @@
       <c r="E37" t="s">
         <v>23</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>61</v>
       </c>
@@ -3051,11 +3135,11 @@
       <c r="E38" t="s">
         <v>24</v>
       </c>
-      <c r="G38" t="s">
+      <c r="H38" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>61</v>
       </c>
@@ -3071,11 +3155,11 @@
       <c r="E39" t="s">
         <v>25</v>
       </c>
-      <c r="G39" t="s">
+      <c r="H39" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>61</v>
       </c>
@@ -3091,11 +3175,11 @@
       <c r="E40" t="s">
         <v>26</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>61</v>
       </c>
@@ -3111,11 +3195,11 @@
       <c r="E41" t="s">
         <v>27</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>61</v>
       </c>
@@ -3131,14 +3215,14 @@
       <c r="E42" t="s">
         <v>28</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" t="s">
         <v>135</v>
       </c>
-      <c r="K42">
+      <c r="L42">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>61</v>
       </c>
@@ -3154,11 +3238,11 @@
       <c r="E43" t="s">
         <v>29</v>
       </c>
-      <c r="G43" t="s">
+      <c r="H43" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>61</v>
       </c>
@@ -3174,14 +3258,14 @@
       <c r="E44" t="s">
         <v>30</v>
       </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
         <v>135</v>
       </c>
-      <c r="H44">
+      <c r="I44">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>61</v>
       </c>
@@ -3197,11 +3281,11 @@
       <c r="E45" t="s">
         <v>31</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>61</v>
       </c>
@@ -3217,11 +3301,11 @@
       <c r="E46" t="s">
         <v>33</v>
       </c>
-      <c r="G46" t="s">
+      <c r="H46" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>61</v>
       </c>
@@ -3237,14 +3321,14 @@
       <c r="E47" t="s">
         <v>34</v>
       </c>
-      <c r="G47" t="s">
+      <c r="H47" t="s">
         <v>135</v>
       </c>
-      <c r="H47">
+      <c r="I47">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>61</v>
       </c>
@@ -3260,14 +3344,14 @@
       <c r="E48" t="s">
         <v>35</v>
       </c>
-      <c r="G48" t="s">
+      <c r="H48" t="s">
         <v>135</v>
       </c>
-      <c r="J48">
+      <c r="K48">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>61</v>
       </c>
@@ -3283,14 +3367,14 @@
       <c r="E49" t="s">
         <v>37</v>
       </c>
-      <c r="G49" t="s">
+      <c r="H49" t="s">
         <v>135</v>
       </c>
-      <c r="I49">
+      <c r="J49">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>61</v>
       </c>
@@ -3306,11 +3390,11 @@
       <c r="E50" t="s">
         <v>38</v>
       </c>
-      <c r="G50" t="s">
+      <c r="H50" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>61</v>
       </c>
@@ -3326,11 +3410,11 @@
       <c r="E51" t="s">
         <v>39</v>
       </c>
-      <c r="G51" t="s">
+      <c r="H51" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>61</v>
       </c>
@@ -3346,11 +3430,11 @@
       <c r="E52" t="s">
         <v>40</v>
       </c>
-      <c r="G52" t="s">
+      <c r="H52" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>61</v>
       </c>
@@ -3366,11 +3450,11 @@
       <c r="E53" t="s">
         <v>41</v>
       </c>
-      <c r="G53" t="s">
+      <c r="H53" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>65</v>
       </c>
@@ -3387,7 +3471,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>65</v>
       </c>
@@ -3404,7 +3488,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>65</v>
       </c>
@@ -3421,7 +3505,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>65</v>
       </c>
@@ -3438,7 +3522,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -3455,7 +3539,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>65</v>
       </c>
@@ -3472,7 +3556,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>65</v>
       </c>
@@ -3489,7 +3573,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>65</v>
       </c>
@@ -3506,7 +3590,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>65</v>
       </c>
@@ -3523,7 +3607,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>65</v>
       </c>
@@ -3540,7 +3624,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>65</v>
       </c>

--- a/SVTwello/zondag2.xlsx
+++ b/SVTwello/zondag2.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B82CBA0-BC4C-734C-A3EF-438BF231BD3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20580" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20580" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="spelers" sheetId="1" r:id="rId1"/>

--- a/SVTwello/zondag2.xlsx
+++ b/SVTwello/zondag2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rodi/Documents/Zondag2/SVTwello/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2093CBFC-A7B1-7242-8657-BDD58CE78927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{495F2F21-450C-6648-97BC-757DF2E663B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34160" windowHeight="20180" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34160" windowHeight="20180" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="spelers" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3038" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2985" uniqueCount="198">
   <si>
     <t>wedstrijd_id</t>
   </si>
@@ -432,9 +432,6 @@
     <t>aanwezig</t>
   </si>
   <si>
-    <t>status</t>
-  </si>
-  <si>
     <t>doelpunten</t>
   </si>
   <si>
@@ -448,18 +445,6 @@
   </si>
   <si>
     <t>penalty</t>
-  </si>
-  <si>
-    <t>Volledig</t>
-  </si>
-  <si>
-    <t>Niet gespeeld</t>
-  </si>
-  <si>
-    <t>Afwezig</t>
-  </si>
-  <si>
-    <t>Deels</t>
   </si>
   <si>
     <t>speler naam</t>
@@ -2215,7 +2200,7 @@
         <v>80</v>
       </c>
       <c r="C1" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -2258,7 +2243,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:M651"/>
+  <dimension ref="A1:L651"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -2273,7 +2258,7 @@
     <col min="13" max="13" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2290,31 +2275,28 @@
         <v>133</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>134</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="L1" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="M1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -2351,11 +2333,8 @@
       <c r="L2" s="3">
         <v>0</v>
       </c>
-      <c r="M2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -2392,11 +2371,8 @@
       <c r="L3" s="3">
         <v>0</v>
       </c>
-      <c r="M3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -2433,11 +2409,8 @@
       <c r="L4" s="3">
         <v>0</v>
       </c>
-      <c r="M4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -2474,11 +2447,8 @@
       <c r="L5" s="3">
         <v>0</v>
       </c>
-      <c r="M5" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -2515,11 +2485,8 @@
       <c r="L6" s="3">
         <v>1</v>
       </c>
-      <c r="M6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -2556,11 +2523,8 @@
       <c r="L7" s="3">
         <v>0</v>
       </c>
-      <c r="M7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -2597,11 +2561,8 @@
       <c r="L8" s="3">
         <v>0</v>
       </c>
-      <c r="M8" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -2638,11 +2599,8 @@
       <c r="L9" s="3">
         <v>0</v>
       </c>
-      <c r="M9" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -2679,11 +2637,8 @@
       <c r="L10" s="3">
         <v>0</v>
       </c>
-      <c r="M10" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -2720,11 +2675,8 @@
       <c r="L11" s="3">
         <v>0</v>
       </c>
-      <c r="M11" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -2761,11 +2713,8 @@
       <c r="L12" s="3">
         <v>0</v>
       </c>
-      <c r="M12" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -2802,11 +2751,8 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -2843,11 +2789,8 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -2884,11 +2827,8 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -2925,11 +2865,8 @@
       <c r="L16" s="3">
         <v>0</v>
       </c>
-      <c r="M16" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -2966,11 +2903,8 @@
       <c r="L17" s="3">
         <v>0</v>
       </c>
-      <c r="M17" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -3007,11 +2941,8 @@
       <c r="L18" s="3">
         <v>0</v>
       </c>
-      <c r="M18" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -3048,11 +2979,8 @@
       <c r="L19" s="3">
         <v>0</v>
       </c>
-      <c r="M19" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -3089,11 +3017,8 @@
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -3130,11 +3055,8 @@
       <c r="L21" s="3">
         <v>0</v>
       </c>
-      <c r="M21" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -3171,11 +3093,8 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -3212,11 +3131,8 @@
       <c r="L23" s="3">
         <v>0</v>
       </c>
-      <c r="M23" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -3253,11 +3169,8 @@
       <c r="L24" s="3">
         <v>0</v>
       </c>
-      <c r="M24" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -3294,11 +3207,8 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>7</v>
       </c>
@@ -3335,11 +3245,8 @@
       <c r="L26" s="3">
         <v>0</v>
       </c>
-      <c r="M26" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>7</v>
       </c>
@@ -3376,11 +3283,8 @@
       <c r="L27" s="3">
         <v>0</v>
       </c>
-      <c r="M27" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>13</v>
       </c>
@@ -3417,11 +3321,8 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>13</v>
       </c>
@@ -3458,11 +3359,8 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>13</v>
       </c>
@@ -3499,11 +3397,8 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>13</v>
       </c>
@@ -3540,11 +3435,8 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>13</v>
       </c>
@@ -3581,11 +3473,8 @@
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>13</v>
       </c>
@@ -3622,11 +3511,8 @@
       <c r="L33" s="3">
         <v>0</v>
       </c>
-      <c r="M33" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>13</v>
       </c>
@@ -3663,11 +3549,8 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>13</v>
       </c>
@@ -3704,11 +3587,8 @@
       <c r="L35" s="3">
         <v>0</v>
       </c>
-      <c r="M35" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>13</v>
       </c>
@@ -3745,11 +3625,8 @@
       <c r="L36" s="3">
         <v>0</v>
       </c>
-      <c r="M36" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>13</v>
       </c>
@@ -3786,11 +3663,8 @@
       <c r="L37" s="3">
         <v>0</v>
       </c>
-      <c r="M37" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>13</v>
       </c>
@@ -3827,11 +3701,8 @@
       <c r="L38" s="3">
         <v>0</v>
       </c>
-      <c r="M38" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>13</v>
       </c>
@@ -3868,11 +3739,8 @@
       <c r="L39" s="3">
         <v>0</v>
       </c>
-      <c r="M39" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>13</v>
       </c>
@@ -3909,11 +3777,8 @@
       <c r="L40" s="3">
         <v>0</v>
       </c>
-      <c r="M40" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>13</v>
       </c>
@@ -3950,11 +3815,8 @@
       <c r="L41" s="3">
         <v>0</v>
       </c>
-      <c r="M41" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>13</v>
       </c>
@@ -3991,11 +3853,8 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>13</v>
       </c>
@@ -4032,11 +3891,8 @@
       <c r="L43" s="3">
         <v>0</v>
       </c>
-      <c r="M43" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>13</v>
       </c>
@@ -4073,11 +3929,8 @@
       <c r="L44" s="3">
         <v>0</v>
       </c>
-      <c r="M44" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>13</v>
       </c>
@@ -4114,11 +3967,8 @@
       <c r="L45" s="3">
         <v>0</v>
       </c>
-      <c r="M45" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>13</v>
       </c>
@@ -4155,11 +4005,8 @@
       <c r="L46" s="3">
         <v>0</v>
       </c>
-      <c r="M46" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>13</v>
       </c>
@@ -4196,11 +4043,8 @@
       <c r="L47" s="3">
         <v>0</v>
       </c>
-      <c r="M47" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>13</v>
       </c>
@@ -4237,11 +4081,8 @@
       <c r="L48" s="3">
         <v>0</v>
       </c>
-      <c r="M48" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>13</v>
       </c>
@@ -4278,11 +4119,8 @@
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>13</v>
       </c>
@@ -4319,11 +4157,8 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>13</v>
       </c>
@@ -4360,11 +4195,8 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>13</v>
       </c>
@@ -4401,11 +4233,8 @@
       <c r="L52" s="3">
         <v>0</v>
       </c>
-      <c r="M52" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>13</v>
       </c>
@@ -4442,11 +4271,8 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>17</v>
       </c>
@@ -4484,7 +4310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>17</v>
       </c>
@@ -4522,7 +4348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>17</v>
       </c>
@@ -4560,7 +4386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>17</v>
       </c>
@@ -4598,7 +4424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>17</v>
       </c>
@@ -4636,7 +4462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -4674,7 +4500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>17</v>
       </c>
@@ -4712,7 +4538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>17</v>
       </c>
@@ -4750,7 +4576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>17</v>
       </c>
@@ -4788,7 +4614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>17</v>
       </c>
@@ -4826,7 +4652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>17</v>
       </c>
@@ -27202,172 +27028,172 @@
         <v>78</v>
       </c>
       <c r="B1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G1" t="s">
         <v>145</v>
       </c>
-      <c r="C1" t="s">
+      <c r="H1" t="s">
         <v>146</v>
       </c>
-      <c r="D1" t="s">
+      <c r="I1" t="s">
         <v>147</v>
       </c>
-      <c r="E1" t="s">
+      <c r="J1" t="s">
         <v>148</v>
       </c>
-      <c r="F1" t="s">
+      <c r="K1" t="s">
         <v>149</v>
       </c>
-      <c r="G1" t="s">
+      <c r="L1" t="s">
         <v>150</v>
       </c>
-      <c r="H1" t="s">
+      <c r="M1" t="s">
         <v>151</v>
       </c>
-      <c r="I1" t="s">
+      <c r="N1" t="s">
         <v>152</v>
       </c>
-      <c r="J1" t="s">
+      <c r="O1" t="s">
         <v>153</v>
       </c>
-      <c r="K1" t="s">
+      <c r="P1" t="s">
         <v>154</v>
       </c>
-      <c r="L1" t="s">
+      <c r="Q1" t="s">
         <v>155</v>
       </c>
-      <c r="M1" t="s">
+      <c r="R1" t="s">
         <v>156</v>
       </c>
-      <c r="N1" t="s">
+      <c r="S1" t="s">
         <v>157</v>
       </c>
-      <c r="O1" t="s">
+      <c r="T1" t="s">
         <v>158</v>
       </c>
-      <c r="P1" t="s">
+      <c r="U1" t="s">
         <v>159</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="V1" t="s">
         <v>160</v>
       </c>
-      <c r="R1" t="s">
+      <c r="W1" t="s">
         <v>161</v>
       </c>
-      <c r="S1" t="s">
+      <c r="X1" t="s">
         <v>162</v>
       </c>
-      <c r="T1" t="s">
+      <c r="Y1" t="s">
         <v>163</v>
       </c>
-      <c r="U1" t="s">
+      <c r="Z1" t="s">
         <v>164</v>
       </c>
-      <c r="V1" t="s">
+      <c r="AA1" t="s">
         <v>165</v>
       </c>
-      <c r="W1" t="s">
+      <c r="AB1" t="s">
         <v>166</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AC1" t="s">
         <v>167</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AD1" t="s">
         <v>168</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AE1" t="s">
         <v>169</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AF1" t="s">
         <v>170</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AG1" t="s">
         <v>171</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AH1" t="s">
         <v>172</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AI1" t="s">
         <v>173</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AJ1" t="s">
         <v>174</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AK1" t="s">
         <v>175</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AL1" t="s">
         <v>176</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AM1" t="s">
         <v>177</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AN1" t="s">
         <v>178</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AO1" t="s">
         <v>179</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AP1" t="s">
         <v>180</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AQ1" t="s">
         <v>181</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AR1" t="s">
         <v>182</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AS1" t="s">
         <v>183</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AT1" t="s">
         <v>184</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AU1" t="s">
         <v>185</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AV1" t="s">
         <v>186</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AW1" t="s">
         <v>187</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AX1" t="s">
         <v>188</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AY1" t="s">
         <v>189</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AZ1" t="s">
         <v>190</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="BA1" t="s">
         <v>191</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="BB1" t="s">
         <v>192</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="BC1" t="s">
         <v>193</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BD1" t="s">
         <v>194</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BE1" t="s">
         <v>195</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>196</v>
-      </c>
-      <c r="BB1" t="s">
-        <v>197</v>
-      </c>
-      <c r="BC1" t="s">
-        <v>198</v>
-      </c>
-      <c r="BD1" t="s">
-        <v>199</v>
-      </c>
-      <c r="BE1" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:57" x14ac:dyDescent="0.2">

--- a/SVTwello/zondag2.xlsx
+++ b/SVTwello/zondag2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rodi/Documents/Zondag2/SVTwello/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{495F2F21-450C-6648-97BC-757DF2E663B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FAC5D64-D0F1-2547-BE60-1B746A0A7761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34160" windowHeight="20180" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2734,7 +2734,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="3">
         <v>0</v>
@@ -3000,7 +3000,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>

--- a/SVTwello/zondag2.xlsx
+++ b/SVTwello/zondag2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rodi/Documents/Zondag2/SVTwello/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FAC5D64-D0F1-2547-BE60-1B746A0A7761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31894BE4-05B1-FA49-955E-CC7A25EAF461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34160" windowHeight="20180" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34160" windowHeight="20180" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="spelers" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2985" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2984" uniqueCount="197">
   <si>
     <t>wedstrijd_id</t>
   </si>
@@ -454,9 +454,6 @@
   </si>
   <si>
     <t>2026-08-09 11:00</t>
-  </si>
-  <si>
-    <t>2026-08-11 20:00</t>
   </si>
   <si>
     <t>2026-08-13 08:00</t>
@@ -2200,7 +2197,7 @@
         <v>80</v>
       </c>
       <c r="C1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -2275,7 +2272,7 @@
         <v>133</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>134</v>
@@ -27015,15 +27012,15 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:BE27"/>
+  <dimension ref="A1:BD27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>78</v>
       </c>
@@ -27192,11 +27189,8 @@
       <c r="BD1" t="s">
         <v>194</v>
       </c>
-      <c r="BE1" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="2" spans="1:57" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -27365,11 +27359,8 @@
       <c r="BD2">
         <v>0</v>
       </c>
-      <c r="BE2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:57" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -27538,11 +27529,8 @@
       <c r="BD3">
         <v>0</v>
       </c>
-      <c r="BE3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:57" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -27711,11 +27699,8 @@
       <c r="BD4">
         <v>0</v>
       </c>
-      <c r="BE4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:57" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -27884,11 +27869,8 @@
       <c r="BD5">
         <v>0</v>
       </c>
-      <c r="BE5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:57" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -28057,11 +28039,8 @@
       <c r="BD6">
         <v>0</v>
       </c>
-      <c r="BE6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:57" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -28230,11 +28209,8 @@
       <c r="BD7">
         <v>0</v>
       </c>
-      <c r="BE7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:57" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -28403,11 +28379,8 @@
       <c r="BD8">
         <v>0</v>
       </c>
-      <c r="BE8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:57" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -28576,11 +28549,8 @@
       <c r="BD9">
         <v>0</v>
       </c>
-      <c r="BE9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:57" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -28749,11 +28719,8 @@
       <c r="BD10">
         <v>0</v>
       </c>
-      <c r="BE10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:57" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -28922,11 +28889,8 @@
       <c r="BD11">
         <v>0</v>
       </c>
-      <c r="BE11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:57" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -29095,11 +29059,8 @@
       <c r="BD12">
         <v>0</v>
       </c>
-      <c r="BE12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:57" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -29268,11 +29229,8 @@
       <c r="BD13">
         <v>0</v>
       </c>
-      <c r="BE13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:57" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -29441,11 +29399,8 @@
       <c r="BD14">
         <v>0</v>
       </c>
-      <c r="BE14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:57" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -29614,11 +29569,8 @@
       <c r="BD15">
         <v>0</v>
       </c>
-      <c r="BE15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:57" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -29787,11 +29739,8 @@
       <c r="BD16">
         <v>0</v>
       </c>
-      <c r="BE16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:57" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -29960,11 +29909,8 @@
       <c r="BD17">
         <v>0</v>
       </c>
-      <c r="BE17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:57" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -30133,11 +30079,8 @@
       <c r="BD18">
         <v>0</v>
       </c>
-      <c r="BE18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:57" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -30306,11 +30249,8 @@
       <c r="BD19">
         <v>0</v>
       </c>
-      <c r="BE19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:57" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -30479,11 +30419,8 @@
       <c r="BD20">
         <v>0</v>
       </c>
-      <c r="BE20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:57" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -30652,11 +30589,8 @@
       <c r="BD21">
         <v>0</v>
       </c>
-      <c r="BE21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:57" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -30825,11 +30759,8 @@
       <c r="BD22">
         <v>0</v>
       </c>
-      <c r="BE22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:57" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -30998,11 +30929,8 @@
       <c r="BD23">
         <v>0</v>
       </c>
-      <c r="BE23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:57" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -31171,11 +31099,8 @@
       <c r="BD24">
         <v>0</v>
       </c>
-      <c r="BE24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:57" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -31344,11 +31269,8 @@
       <c r="BD25">
         <v>0</v>
       </c>
-      <c r="BE25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:57" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -31517,11 +31439,8 @@
       <c r="BD26">
         <v>0</v>
       </c>
-      <c r="BE26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:57" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -31688,9 +31607,6 @@
         <v>0</v>
       </c>
       <c r="BD27">
-        <v>0</v>
-      </c>
-      <c r="BE27">
         <v>0</v>
       </c>
     </row>
@@ -31707,8 +31623,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:BE27">
-    <cfRule type="colorScale" priority="4">
+  <conditionalFormatting sqref="C2:BD27">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
